--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -60530,632 +60530,632 @@
     <mergeCell ref="AG5:AG6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId506751"/>
-    <hyperlink ref="A8" r:id="rId506752"/>
-    <hyperlink ref="A9" r:id="rId506753"/>
-    <hyperlink ref="A10" r:id="rId506754"/>
-    <hyperlink ref="A11" r:id="rId506755"/>
-    <hyperlink ref="A12" r:id="rId506756"/>
-    <hyperlink ref="A13" r:id="rId506757"/>
-    <hyperlink ref="A14" r:id="rId506758"/>
-    <hyperlink ref="A15" r:id="rId506759"/>
-    <hyperlink ref="A16" r:id="rId506760"/>
-    <hyperlink ref="A17" r:id="rId506761"/>
-    <hyperlink ref="A18" r:id="rId506762"/>
-    <hyperlink ref="A19" r:id="rId506763"/>
-    <hyperlink ref="A20" r:id="rId506764"/>
-    <hyperlink ref="A21" r:id="rId506765"/>
-    <hyperlink ref="A22" r:id="rId506766"/>
-    <hyperlink ref="A23" r:id="rId506767"/>
-    <hyperlink ref="A24" r:id="rId506768"/>
-    <hyperlink ref="A25" r:id="rId506769"/>
-    <hyperlink ref="A26" r:id="rId506770"/>
-    <hyperlink ref="A27" r:id="rId506771"/>
-    <hyperlink ref="A28" r:id="rId506772"/>
-    <hyperlink ref="A29" r:id="rId506773"/>
-    <hyperlink ref="A30" r:id="rId506774"/>
-    <hyperlink ref="A31" r:id="rId506775"/>
-    <hyperlink ref="A32" r:id="rId506776"/>
-    <hyperlink ref="A33" r:id="rId506777"/>
-    <hyperlink ref="A34" r:id="rId506778"/>
-    <hyperlink ref="A35" r:id="rId506779"/>
-    <hyperlink ref="A36" r:id="rId506780"/>
-    <hyperlink ref="A37" r:id="rId506781"/>
-    <hyperlink ref="A38" r:id="rId506782"/>
-    <hyperlink ref="A39" r:id="rId506783"/>
-    <hyperlink ref="A40" r:id="rId506784"/>
-    <hyperlink ref="A41" r:id="rId506785"/>
-    <hyperlink ref="A42" r:id="rId506786"/>
-    <hyperlink ref="A43" r:id="rId506787"/>
-    <hyperlink ref="A44" r:id="rId506788"/>
-    <hyperlink ref="A45" r:id="rId506789"/>
-    <hyperlink ref="A46" r:id="rId506790"/>
-    <hyperlink ref="A47" r:id="rId506791"/>
-    <hyperlink ref="A48" r:id="rId506792"/>
-    <hyperlink ref="A49" r:id="rId506793"/>
-    <hyperlink ref="A50" r:id="rId506794"/>
-    <hyperlink ref="A51" r:id="rId506795"/>
-    <hyperlink ref="A52" r:id="rId506796"/>
-    <hyperlink ref="A53" r:id="rId506797"/>
-    <hyperlink ref="A54" r:id="rId506798"/>
-    <hyperlink ref="A55" r:id="rId506799"/>
-    <hyperlink ref="A56" r:id="rId506800"/>
-    <hyperlink ref="A57" r:id="rId506801"/>
-    <hyperlink ref="A58" r:id="rId506802"/>
-    <hyperlink ref="A59" r:id="rId506803"/>
-    <hyperlink ref="A60" r:id="rId506804"/>
-    <hyperlink ref="A61" r:id="rId506805"/>
-    <hyperlink ref="A62" r:id="rId506806"/>
-    <hyperlink ref="A63" r:id="rId506807"/>
-    <hyperlink ref="A64" r:id="rId506808"/>
-    <hyperlink ref="A65" r:id="rId506809"/>
-    <hyperlink ref="A66" r:id="rId506810"/>
-    <hyperlink ref="A67" r:id="rId506811"/>
-    <hyperlink ref="A68" r:id="rId506812"/>
-    <hyperlink ref="A69" r:id="rId506813"/>
-    <hyperlink ref="A70" r:id="rId506814"/>
-    <hyperlink ref="A71" r:id="rId506815"/>
-    <hyperlink ref="A72" r:id="rId506816"/>
-    <hyperlink ref="A73" r:id="rId506817"/>
-    <hyperlink ref="A74" r:id="rId506818"/>
-    <hyperlink ref="A75" r:id="rId506819"/>
-    <hyperlink ref="A76" r:id="rId506820"/>
-    <hyperlink ref="A77" r:id="rId506821"/>
-    <hyperlink ref="A78" r:id="rId506822"/>
-    <hyperlink ref="A79" r:id="rId506823"/>
-    <hyperlink ref="A80" r:id="rId506824"/>
-    <hyperlink ref="A81" r:id="rId506825"/>
-    <hyperlink ref="A82" r:id="rId506826"/>
-    <hyperlink ref="A83" r:id="rId506827"/>
-    <hyperlink ref="A84" r:id="rId506828"/>
-    <hyperlink ref="A85" r:id="rId506829"/>
-    <hyperlink ref="A86" r:id="rId506830"/>
-    <hyperlink ref="A87" r:id="rId506831"/>
-    <hyperlink ref="A88" r:id="rId506832"/>
-    <hyperlink ref="A89" r:id="rId506833"/>
-    <hyperlink ref="A90" r:id="rId506834"/>
-    <hyperlink ref="A91" r:id="rId506835"/>
-    <hyperlink ref="A92" r:id="rId506836"/>
-    <hyperlink ref="A93" r:id="rId506837"/>
-    <hyperlink ref="A94" r:id="rId506838"/>
-    <hyperlink ref="A95" r:id="rId506839"/>
-    <hyperlink ref="A96" r:id="rId506840"/>
-    <hyperlink ref="A97" r:id="rId506841"/>
-    <hyperlink ref="A98" r:id="rId506842"/>
-    <hyperlink ref="A99" r:id="rId506843"/>
-    <hyperlink ref="A100" r:id="rId506844"/>
-    <hyperlink ref="A101" r:id="rId506845"/>
-    <hyperlink ref="A102" r:id="rId506846"/>
-    <hyperlink ref="A103" r:id="rId506847"/>
-    <hyperlink ref="A104" r:id="rId506848"/>
-    <hyperlink ref="A105" r:id="rId506849"/>
-    <hyperlink ref="A106" r:id="rId506850"/>
-    <hyperlink ref="A107" r:id="rId506851"/>
-    <hyperlink ref="A108" r:id="rId506852"/>
-    <hyperlink ref="A109" r:id="rId506853"/>
-    <hyperlink ref="A110" r:id="rId506854"/>
-    <hyperlink ref="A111" r:id="rId506855"/>
-    <hyperlink ref="A112" r:id="rId506856"/>
-    <hyperlink ref="A113" r:id="rId506857"/>
-    <hyperlink ref="A114" r:id="rId506858"/>
-    <hyperlink ref="A115" r:id="rId506859"/>
-    <hyperlink ref="A116" r:id="rId506860"/>
-    <hyperlink ref="A117" r:id="rId506861"/>
-    <hyperlink ref="A118" r:id="rId506862"/>
-    <hyperlink ref="A119" r:id="rId506863"/>
-    <hyperlink ref="A120" r:id="rId506864"/>
-    <hyperlink ref="A121" r:id="rId506865"/>
-    <hyperlink ref="A122" r:id="rId506866"/>
-    <hyperlink ref="A123" r:id="rId506867"/>
-    <hyperlink ref="A124" r:id="rId506868"/>
-    <hyperlink ref="A125" r:id="rId506869"/>
-    <hyperlink ref="A126" r:id="rId506870"/>
-    <hyperlink ref="A127" r:id="rId506871"/>
-    <hyperlink ref="A128" r:id="rId506872"/>
-    <hyperlink ref="A129" r:id="rId506873"/>
-    <hyperlink ref="A130" r:id="rId506874"/>
-    <hyperlink ref="A131" r:id="rId506875"/>
-    <hyperlink ref="A132" r:id="rId506876"/>
-    <hyperlink ref="A133" r:id="rId506877"/>
-    <hyperlink ref="A134" r:id="rId506878"/>
-    <hyperlink ref="A135" r:id="rId506879"/>
-    <hyperlink ref="A136" r:id="rId506880"/>
-    <hyperlink ref="A137" r:id="rId506881"/>
-    <hyperlink ref="A138" r:id="rId506882"/>
-    <hyperlink ref="A139" r:id="rId506883"/>
-    <hyperlink ref="A140" r:id="rId506884"/>
-    <hyperlink ref="A141" r:id="rId506885"/>
-    <hyperlink ref="A142" r:id="rId506886"/>
-    <hyperlink ref="A143" r:id="rId506887"/>
-    <hyperlink ref="A144" r:id="rId506888"/>
-    <hyperlink ref="A145" r:id="rId506889"/>
-    <hyperlink ref="A146" r:id="rId506890"/>
-    <hyperlink ref="A147" r:id="rId506891"/>
-    <hyperlink ref="A148" r:id="rId506892"/>
-    <hyperlink ref="A149" r:id="rId506893"/>
-    <hyperlink ref="A150" r:id="rId506894"/>
-    <hyperlink ref="A151" r:id="rId506895"/>
-    <hyperlink ref="A152" r:id="rId506896"/>
-    <hyperlink ref="A153" r:id="rId506897"/>
-    <hyperlink ref="A154" r:id="rId506898"/>
-    <hyperlink ref="A155" r:id="rId506899"/>
-    <hyperlink ref="A156" r:id="rId506900"/>
-    <hyperlink ref="A157" r:id="rId506901"/>
-    <hyperlink ref="A158" r:id="rId506902"/>
-    <hyperlink ref="A159" r:id="rId506903"/>
-    <hyperlink ref="A160" r:id="rId506904"/>
-    <hyperlink ref="A161" r:id="rId506905"/>
-    <hyperlink ref="A162" r:id="rId506906"/>
-    <hyperlink ref="A163" r:id="rId506907"/>
-    <hyperlink ref="A164" r:id="rId506908"/>
-    <hyperlink ref="A165" r:id="rId506909"/>
-    <hyperlink ref="A166" r:id="rId506910"/>
-    <hyperlink ref="A167" r:id="rId506911"/>
-    <hyperlink ref="A168" r:id="rId506912"/>
-    <hyperlink ref="A169" r:id="rId506913"/>
-    <hyperlink ref="A170" r:id="rId506914"/>
-    <hyperlink ref="A171" r:id="rId506915"/>
-    <hyperlink ref="A172" r:id="rId506916"/>
-    <hyperlink ref="A173" r:id="rId506917"/>
-    <hyperlink ref="A174" r:id="rId506918"/>
-    <hyperlink ref="A175" r:id="rId506919"/>
-    <hyperlink ref="A176" r:id="rId506920"/>
-    <hyperlink ref="A177" r:id="rId506921"/>
-    <hyperlink ref="A178" r:id="rId506922"/>
-    <hyperlink ref="A179" r:id="rId506923"/>
-    <hyperlink ref="A180" r:id="rId506924"/>
-    <hyperlink ref="A181" r:id="rId506925"/>
-    <hyperlink ref="A182" r:id="rId506926"/>
-    <hyperlink ref="A183" r:id="rId506927"/>
-    <hyperlink ref="A184" r:id="rId506928"/>
-    <hyperlink ref="A185" r:id="rId506929"/>
-    <hyperlink ref="A186" r:id="rId506930"/>
-    <hyperlink ref="A187" r:id="rId506931"/>
-    <hyperlink ref="A188" r:id="rId506932"/>
-    <hyperlink ref="A189" r:id="rId506933"/>
-    <hyperlink ref="A190" r:id="rId506934"/>
-    <hyperlink ref="A191" r:id="rId506935"/>
-    <hyperlink ref="A192" r:id="rId506936"/>
-    <hyperlink ref="A193" r:id="rId506937"/>
-    <hyperlink ref="A194" r:id="rId506938"/>
-    <hyperlink ref="A195" r:id="rId506939"/>
-    <hyperlink ref="A196" r:id="rId506940"/>
-    <hyperlink ref="A197" r:id="rId506941"/>
-    <hyperlink ref="A198" r:id="rId506942"/>
-    <hyperlink ref="A199" r:id="rId506943"/>
-    <hyperlink ref="A200" r:id="rId506944"/>
-    <hyperlink ref="A201" r:id="rId506945"/>
-    <hyperlink ref="A202" r:id="rId506946"/>
-    <hyperlink ref="A203" r:id="rId506947"/>
-    <hyperlink ref="A204" r:id="rId506948"/>
-    <hyperlink ref="A205" r:id="rId506949"/>
-    <hyperlink ref="A206" r:id="rId506950"/>
-    <hyperlink ref="A207" r:id="rId506951"/>
-    <hyperlink ref="A208" r:id="rId506952"/>
-    <hyperlink ref="A209" r:id="rId506953"/>
-    <hyperlink ref="A210" r:id="rId506954"/>
-    <hyperlink ref="A211" r:id="rId506955"/>
-    <hyperlink ref="A212" r:id="rId506956"/>
-    <hyperlink ref="A213" r:id="rId506957"/>
-    <hyperlink ref="A214" r:id="rId506958"/>
-    <hyperlink ref="A215" r:id="rId506959"/>
-    <hyperlink ref="A216" r:id="rId506960"/>
-    <hyperlink ref="A217" r:id="rId506961"/>
-    <hyperlink ref="A218" r:id="rId506962"/>
-    <hyperlink ref="A219" r:id="rId506963"/>
-    <hyperlink ref="A220" r:id="rId506964"/>
-    <hyperlink ref="A221" r:id="rId506965"/>
-    <hyperlink ref="A222" r:id="rId506966"/>
-    <hyperlink ref="A223" r:id="rId506967"/>
-    <hyperlink ref="A224" r:id="rId506968"/>
-    <hyperlink ref="A225" r:id="rId506969"/>
-    <hyperlink ref="A226" r:id="rId506970"/>
-    <hyperlink ref="A227" r:id="rId506971"/>
-    <hyperlink ref="A228" r:id="rId506972"/>
-    <hyperlink ref="A229" r:id="rId506973"/>
-    <hyperlink ref="A230" r:id="rId506974"/>
-    <hyperlink ref="A231" r:id="rId506975"/>
-    <hyperlink ref="A232" r:id="rId506976"/>
-    <hyperlink ref="A233" r:id="rId506977"/>
-    <hyperlink ref="A234" r:id="rId506978"/>
-    <hyperlink ref="A235" r:id="rId506979"/>
-    <hyperlink ref="A236" r:id="rId506980"/>
-    <hyperlink ref="A237" r:id="rId506981"/>
-    <hyperlink ref="A238" r:id="rId506982"/>
-    <hyperlink ref="A239" r:id="rId506983"/>
-    <hyperlink ref="A240" r:id="rId506984"/>
-    <hyperlink ref="A241" r:id="rId506985"/>
-    <hyperlink ref="A242" r:id="rId506986"/>
-    <hyperlink ref="A243" r:id="rId506987"/>
-    <hyperlink ref="A244" r:id="rId506988"/>
-    <hyperlink ref="A245" r:id="rId506989"/>
-    <hyperlink ref="A246" r:id="rId506990"/>
-    <hyperlink ref="A247" r:id="rId506991"/>
-    <hyperlink ref="A248" r:id="rId506992"/>
-    <hyperlink ref="A249" r:id="rId506993"/>
-    <hyperlink ref="A250" r:id="rId506994"/>
-    <hyperlink ref="A251" r:id="rId506995"/>
-    <hyperlink ref="A252" r:id="rId506996"/>
-    <hyperlink ref="A253" r:id="rId506997"/>
-    <hyperlink ref="A254" r:id="rId506998"/>
-    <hyperlink ref="A255" r:id="rId506999"/>
-    <hyperlink ref="A256" r:id="rId507000"/>
-    <hyperlink ref="A257" r:id="rId507001"/>
-    <hyperlink ref="A258" r:id="rId507002"/>
-    <hyperlink ref="A259" r:id="rId507003"/>
-    <hyperlink ref="A260" r:id="rId507004"/>
-    <hyperlink ref="A261" r:id="rId507005"/>
-    <hyperlink ref="A262" r:id="rId507006"/>
-    <hyperlink ref="A263" r:id="rId507007"/>
-    <hyperlink ref="A264" r:id="rId507008"/>
-    <hyperlink ref="A265" r:id="rId507009"/>
-    <hyperlink ref="A266" r:id="rId507010"/>
-    <hyperlink ref="A267" r:id="rId507011"/>
-    <hyperlink ref="A268" r:id="rId507012"/>
-    <hyperlink ref="A269" r:id="rId507013"/>
-    <hyperlink ref="A270" r:id="rId507014"/>
-    <hyperlink ref="A271" r:id="rId507015"/>
-    <hyperlink ref="A272" r:id="rId507016"/>
-    <hyperlink ref="A273" r:id="rId507017"/>
-    <hyperlink ref="A274" r:id="rId507018"/>
-    <hyperlink ref="A275" r:id="rId507019"/>
-    <hyperlink ref="A276" r:id="rId507020"/>
-    <hyperlink ref="A277" r:id="rId507021"/>
-    <hyperlink ref="A278" r:id="rId507022"/>
-    <hyperlink ref="A279" r:id="rId507023"/>
-    <hyperlink ref="A280" r:id="rId507024"/>
-    <hyperlink ref="A281" r:id="rId507025"/>
-    <hyperlink ref="A282" r:id="rId507026"/>
-    <hyperlink ref="A283" r:id="rId507027"/>
-    <hyperlink ref="A284" r:id="rId507028"/>
-    <hyperlink ref="A285" r:id="rId507029"/>
-    <hyperlink ref="A286" r:id="rId507030"/>
-    <hyperlink ref="A287" r:id="rId507031"/>
-    <hyperlink ref="A288" r:id="rId507032"/>
-    <hyperlink ref="A289" r:id="rId507033"/>
-    <hyperlink ref="A290" r:id="rId507034"/>
-    <hyperlink ref="A291" r:id="rId507035"/>
-    <hyperlink ref="A292" r:id="rId507036"/>
-    <hyperlink ref="A293" r:id="rId507037"/>
-    <hyperlink ref="A294" r:id="rId507038"/>
-    <hyperlink ref="A295" r:id="rId507039"/>
-    <hyperlink ref="A296" r:id="rId507040"/>
-    <hyperlink ref="A297" r:id="rId507041"/>
-    <hyperlink ref="A298" r:id="rId507042"/>
-    <hyperlink ref="A299" r:id="rId507043"/>
-    <hyperlink ref="A300" r:id="rId507044"/>
-    <hyperlink ref="A301" r:id="rId507045"/>
-    <hyperlink ref="A302" r:id="rId507046"/>
-    <hyperlink ref="A303" r:id="rId507047"/>
-    <hyperlink ref="A304" r:id="rId507048"/>
-    <hyperlink ref="A305" r:id="rId507049"/>
-    <hyperlink ref="A306" r:id="rId507050"/>
-    <hyperlink ref="A307" r:id="rId507051"/>
-    <hyperlink ref="A308" r:id="rId507052"/>
-    <hyperlink ref="A309" r:id="rId507053"/>
-    <hyperlink ref="A310" r:id="rId507054"/>
-    <hyperlink ref="A311" r:id="rId507055"/>
-    <hyperlink ref="A312" r:id="rId507056"/>
-    <hyperlink ref="A313" r:id="rId507057"/>
-    <hyperlink ref="A314" r:id="rId507058"/>
-    <hyperlink ref="A315" r:id="rId507059"/>
-    <hyperlink ref="A316" r:id="rId507060"/>
-    <hyperlink ref="A317" r:id="rId507061"/>
-    <hyperlink ref="A318" r:id="rId507062"/>
-    <hyperlink ref="A319" r:id="rId507063"/>
-    <hyperlink ref="A320" r:id="rId507064"/>
-    <hyperlink ref="A321" r:id="rId507065"/>
-    <hyperlink ref="A322" r:id="rId507066"/>
-    <hyperlink ref="A323" r:id="rId507067"/>
-    <hyperlink ref="A324" r:id="rId507068"/>
-    <hyperlink ref="A325" r:id="rId507069"/>
-    <hyperlink ref="A326" r:id="rId507070"/>
-    <hyperlink ref="A327" r:id="rId507071"/>
-    <hyperlink ref="A328" r:id="rId507072"/>
-    <hyperlink ref="A329" r:id="rId507073"/>
-    <hyperlink ref="A330" r:id="rId507074"/>
-    <hyperlink ref="A331" r:id="rId507075"/>
-    <hyperlink ref="A332" r:id="rId507076"/>
-    <hyperlink ref="A333" r:id="rId507077"/>
-    <hyperlink ref="A334" r:id="rId507078"/>
-    <hyperlink ref="A335" r:id="rId507079"/>
-    <hyperlink ref="A336" r:id="rId507080"/>
-    <hyperlink ref="A337" r:id="rId507081"/>
-    <hyperlink ref="A338" r:id="rId507082"/>
-    <hyperlink ref="A339" r:id="rId507083"/>
-    <hyperlink ref="A340" r:id="rId507084"/>
-    <hyperlink ref="A341" r:id="rId507085"/>
-    <hyperlink ref="A342" r:id="rId507086"/>
-    <hyperlink ref="A343" r:id="rId507087"/>
-    <hyperlink ref="A344" r:id="rId507088"/>
-    <hyperlink ref="A345" r:id="rId507089"/>
-    <hyperlink ref="A346" r:id="rId507090"/>
-    <hyperlink ref="A347" r:id="rId507091"/>
-    <hyperlink ref="A348" r:id="rId507092"/>
-    <hyperlink ref="A349" r:id="rId507093"/>
-    <hyperlink ref="A350" r:id="rId507094"/>
-    <hyperlink ref="A351" r:id="rId507095"/>
-    <hyperlink ref="A352" r:id="rId507096"/>
-    <hyperlink ref="A353" r:id="rId507097"/>
-    <hyperlink ref="A354" r:id="rId507098"/>
-    <hyperlink ref="A355" r:id="rId507099"/>
-    <hyperlink ref="A356" r:id="rId507100"/>
-    <hyperlink ref="A357" r:id="rId507101"/>
-    <hyperlink ref="A358" r:id="rId507102"/>
-    <hyperlink ref="A359" r:id="rId507103"/>
-    <hyperlink ref="A360" r:id="rId507104"/>
-    <hyperlink ref="A361" r:id="rId507105"/>
-    <hyperlink ref="A362" r:id="rId507106"/>
-    <hyperlink ref="A363" r:id="rId507107"/>
-    <hyperlink ref="A364" r:id="rId507108"/>
-    <hyperlink ref="A365" r:id="rId507109"/>
-    <hyperlink ref="A366" r:id="rId507110"/>
-    <hyperlink ref="A367" r:id="rId507111"/>
-    <hyperlink ref="A368" r:id="rId507112"/>
-    <hyperlink ref="A369" r:id="rId507113"/>
-    <hyperlink ref="A370" r:id="rId507114"/>
-    <hyperlink ref="A371" r:id="rId507115"/>
-    <hyperlink ref="A372" r:id="rId507116"/>
-    <hyperlink ref="A373" r:id="rId507117"/>
-    <hyperlink ref="A374" r:id="rId507118"/>
-    <hyperlink ref="A375" r:id="rId507119"/>
-    <hyperlink ref="A376" r:id="rId507120"/>
-    <hyperlink ref="A377" r:id="rId507121"/>
-    <hyperlink ref="A378" r:id="rId507122"/>
-    <hyperlink ref="A379" r:id="rId507123"/>
-    <hyperlink ref="A380" r:id="rId507124"/>
-    <hyperlink ref="A381" r:id="rId507125"/>
-    <hyperlink ref="A382" r:id="rId507126"/>
-    <hyperlink ref="A383" r:id="rId507127"/>
-    <hyperlink ref="A384" r:id="rId507128"/>
-    <hyperlink ref="A385" r:id="rId507129"/>
-    <hyperlink ref="A386" r:id="rId507130"/>
-    <hyperlink ref="A387" r:id="rId507131"/>
-    <hyperlink ref="A388" r:id="rId507132"/>
-    <hyperlink ref="A389" r:id="rId507133"/>
-    <hyperlink ref="A390" r:id="rId507134"/>
-    <hyperlink ref="A391" r:id="rId507135"/>
-    <hyperlink ref="A392" r:id="rId507136"/>
-    <hyperlink ref="A393" r:id="rId507137"/>
-    <hyperlink ref="A394" r:id="rId507138"/>
-    <hyperlink ref="A395" r:id="rId507139"/>
-    <hyperlink ref="A396" r:id="rId507140"/>
-    <hyperlink ref="A397" r:id="rId507141"/>
-    <hyperlink ref="A398" r:id="rId507142"/>
-    <hyperlink ref="A399" r:id="rId507143"/>
-    <hyperlink ref="A400" r:id="rId507144"/>
-    <hyperlink ref="A401" r:id="rId507145"/>
-    <hyperlink ref="A402" r:id="rId507146"/>
-    <hyperlink ref="A403" r:id="rId507147"/>
-    <hyperlink ref="A404" r:id="rId507148"/>
-    <hyperlink ref="A405" r:id="rId507149"/>
-    <hyperlink ref="A406" r:id="rId507150"/>
-    <hyperlink ref="A407" r:id="rId507151"/>
-    <hyperlink ref="A408" r:id="rId507152"/>
-    <hyperlink ref="A409" r:id="rId507153"/>
-    <hyperlink ref="A410" r:id="rId507154"/>
-    <hyperlink ref="A411" r:id="rId507155"/>
-    <hyperlink ref="A412" r:id="rId507156"/>
-    <hyperlink ref="A413" r:id="rId507157"/>
-    <hyperlink ref="A414" r:id="rId507158"/>
-    <hyperlink ref="A415" r:id="rId507159"/>
-    <hyperlink ref="A416" r:id="rId507160"/>
-    <hyperlink ref="A417" r:id="rId507161"/>
-    <hyperlink ref="A418" r:id="rId507162"/>
-    <hyperlink ref="A419" r:id="rId507163"/>
-    <hyperlink ref="A420" r:id="rId507164"/>
-    <hyperlink ref="A421" r:id="rId507165"/>
-    <hyperlink ref="A422" r:id="rId507166"/>
-    <hyperlink ref="A423" r:id="rId507167"/>
-    <hyperlink ref="A424" r:id="rId507168"/>
-    <hyperlink ref="A425" r:id="rId507169"/>
-    <hyperlink ref="A426" r:id="rId507170"/>
-    <hyperlink ref="A427" r:id="rId507171"/>
-    <hyperlink ref="A428" r:id="rId507172"/>
-    <hyperlink ref="A429" r:id="rId507173"/>
-    <hyperlink ref="A430" r:id="rId507174"/>
-    <hyperlink ref="A431" r:id="rId507175"/>
-    <hyperlink ref="A432" r:id="rId507176"/>
-    <hyperlink ref="A433" r:id="rId507177"/>
-    <hyperlink ref="A434" r:id="rId507178"/>
-    <hyperlink ref="A435" r:id="rId507179"/>
-    <hyperlink ref="A436" r:id="rId507180"/>
-    <hyperlink ref="A437" r:id="rId507181"/>
-    <hyperlink ref="A438" r:id="rId507182"/>
-    <hyperlink ref="A439" r:id="rId507183"/>
-    <hyperlink ref="A440" r:id="rId507184"/>
-    <hyperlink ref="A441" r:id="rId507185"/>
-    <hyperlink ref="A442" r:id="rId507186"/>
-    <hyperlink ref="A443" r:id="rId507187"/>
-    <hyperlink ref="A444" r:id="rId507188"/>
-    <hyperlink ref="A445" r:id="rId507189"/>
-    <hyperlink ref="A446" r:id="rId507190"/>
-    <hyperlink ref="A447" r:id="rId507191"/>
-    <hyperlink ref="A448" r:id="rId507192"/>
-    <hyperlink ref="A449" r:id="rId507193"/>
-    <hyperlink ref="A450" r:id="rId507194"/>
-    <hyperlink ref="A451" r:id="rId507195"/>
-    <hyperlink ref="A452" r:id="rId507196"/>
-    <hyperlink ref="A453" r:id="rId507197"/>
-    <hyperlink ref="A454" r:id="rId507198"/>
-    <hyperlink ref="A455" r:id="rId507199"/>
-    <hyperlink ref="A456" r:id="rId507200"/>
-    <hyperlink ref="A457" r:id="rId507201"/>
-    <hyperlink ref="A458" r:id="rId507202"/>
-    <hyperlink ref="A459" r:id="rId507203"/>
-    <hyperlink ref="A460" r:id="rId507204"/>
-    <hyperlink ref="A461" r:id="rId507205"/>
-    <hyperlink ref="A462" r:id="rId507206"/>
-    <hyperlink ref="A463" r:id="rId507207"/>
-    <hyperlink ref="A464" r:id="rId507208"/>
-    <hyperlink ref="A465" r:id="rId507209"/>
-    <hyperlink ref="A466" r:id="rId507210"/>
-    <hyperlink ref="A467" r:id="rId507211"/>
-    <hyperlink ref="A468" r:id="rId507212"/>
-    <hyperlink ref="A469" r:id="rId507213"/>
-    <hyperlink ref="A470" r:id="rId507214"/>
-    <hyperlink ref="A471" r:id="rId507215"/>
-    <hyperlink ref="A472" r:id="rId507216"/>
-    <hyperlink ref="A473" r:id="rId507217"/>
-    <hyperlink ref="A474" r:id="rId507218"/>
-    <hyperlink ref="A475" r:id="rId507219"/>
-    <hyperlink ref="A476" r:id="rId507220"/>
-    <hyperlink ref="A477" r:id="rId507221"/>
-    <hyperlink ref="A478" r:id="rId507222"/>
-    <hyperlink ref="A479" r:id="rId507223"/>
-    <hyperlink ref="A480" r:id="rId507224"/>
-    <hyperlink ref="A481" r:id="rId507225"/>
-    <hyperlink ref="A482" r:id="rId507226"/>
-    <hyperlink ref="A483" r:id="rId507227"/>
-    <hyperlink ref="A484" r:id="rId507228"/>
-    <hyperlink ref="A485" r:id="rId507229"/>
-    <hyperlink ref="A486" r:id="rId507230"/>
-    <hyperlink ref="A487" r:id="rId507231"/>
-    <hyperlink ref="A488" r:id="rId507232"/>
-    <hyperlink ref="A489" r:id="rId507233"/>
-    <hyperlink ref="A490" r:id="rId507234"/>
-    <hyperlink ref="A491" r:id="rId507235"/>
-    <hyperlink ref="A492" r:id="rId507236"/>
-    <hyperlink ref="A493" r:id="rId507237"/>
-    <hyperlink ref="A494" r:id="rId507238"/>
-    <hyperlink ref="A495" r:id="rId507239"/>
-    <hyperlink ref="A496" r:id="rId507240"/>
-    <hyperlink ref="A497" r:id="rId507241"/>
-    <hyperlink ref="A498" r:id="rId507242"/>
-    <hyperlink ref="A499" r:id="rId507243"/>
-    <hyperlink ref="A500" r:id="rId507244"/>
-    <hyperlink ref="A501" r:id="rId507245"/>
-    <hyperlink ref="A502" r:id="rId507246"/>
-    <hyperlink ref="A503" r:id="rId507247"/>
-    <hyperlink ref="A504" r:id="rId507248"/>
-    <hyperlink ref="A505" r:id="rId507249"/>
-    <hyperlink ref="A506" r:id="rId507250"/>
-    <hyperlink ref="A507" r:id="rId507251"/>
-    <hyperlink ref="A508" r:id="rId507252"/>
-    <hyperlink ref="A509" r:id="rId507253"/>
-    <hyperlink ref="A510" r:id="rId507254"/>
-    <hyperlink ref="A511" r:id="rId507255"/>
-    <hyperlink ref="A512" r:id="rId507256"/>
-    <hyperlink ref="A513" r:id="rId507257"/>
-    <hyperlink ref="A514" r:id="rId507258"/>
-    <hyperlink ref="A515" r:id="rId507259"/>
-    <hyperlink ref="A516" r:id="rId507260"/>
-    <hyperlink ref="A517" r:id="rId507261"/>
-    <hyperlink ref="A518" r:id="rId507262"/>
-    <hyperlink ref="A519" r:id="rId507263"/>
-    <hyperlink ref="A520" r:id="rId507264"/>
-    <hyperlink ref="A521" r:id="rId507265"/>
-    <hyperlink ref="A522" r:id="rId507266"/>
-    <hyperlink ref="A523" r:id="rId507267"/>
-    <hyperlink ref="A524" r:id="rId507268"/>
-    <hyperlink ref="A525" r:id="rId507269"/>
-    <hyperlink ref="A526" r:id="rId507270"/>
-    <hyperlink ref="A527" r:id="rId507271"/>
-    <hyperlink ref="A528" r:id="rId507272"/>
-    <hyperlink ref="A529" r:id="rId507273"/>
-    <hyperlink ref="A530" r:id="rId507274"/>
-    <hyperlink ref="A531" r:id="rId507275"/>
-    <hyperlink ref="A532" r:id="rId507276"/>
-    <hyperlink ref="A533" r:id="rId507277"/>
-    <hyperlink ref="A534" r:id="rId507278"/>
-    <hyperlink ref="A535" r:id="rId507279"/>
-    <hyperlink ref="A536" r:id="rId507280"/>
-    <hyperlink ref="A537" r:id="rId507281"/>
-    <hyperlink ref="A538" r:id="rId507282"/>
-    <hyperlink ref="A539" r:id="rId507283"/>
-    <hyperlink ref="A540" r:id="rId507284"/>
-    <hyperlink ref="A541" r:id="rId507285"/>
-    <hyperlink ref="A542" r:id="rId507286"/>
-    <hyperlink ref="A543" r:id="rId507287"/>
-    <hyperlink ref="A544" r:id="rId507288"/>
-    <hyperlink ref="A545" r:id="rId507289"/>
-    <hyperlink ref="A546" r:id="rId507290"/>
-    <hyperlink ref="A547" r:id="rId507291"/>
-    <hyperlink ref="A548" r:id="rId507292"/>
-    <hyperlink ref="A549" r:id="rId507293"/>
-    <hyperlink ref="A550" r:id="rId507294"/>
-    <hyperlink ref="A551" r:id="rId507295"/>
-    <hyperlink ref="A552" r:id="rId507296"/>
-    <hyperlink ref="A553" r:id="rId507297"/>
-    <hyperlink ref="A554" r:id="rId507298"/>
-    <hyperlink ref="A555" r:id="rId507299"/>
-    <hyperlink ref="A556" r:id="rId507300"/>
-    <hyperlink ref="A557" r:id="rId507301"/>
-    <hyperlink ref="A558" r:id="rId507302"/>
-    <hyperlink ref="A559" r:id="rId507303"/>
-    <hyperlink ref="A560" r:id="rId507304"/>
-    <hyperlink ref="A561" r:id="rId507305"/>
-    <hyperlink ref="A562" r:id="rId507306"/>
-    <hyperlink ref="A563" r:id="rId507307"/>
-    <hyperlink ref="A564" r:id="rId507308"/>
-    <hyperlink ref="A565" r:id="rId507309"/>
-    <hyperlink ref="A566" r:id="rId507310"/>
-    <hyperlink ref="A567" r:id="rId507311"/>
-    <hyperlink ref="A568" r:id="rId507312"/>
-    <hyperlink ref="A569" r:id="rId507313"/>
-    <hyperlink ref="A570" r:id="rId507314"/>
-    <hyperlink ref="A571" r:id="rId507315"/>
-    <hyperlink ref="A572" r:id="rId507316"/>
-    <hyperlink ref="A573" r:id="rId507317"/>
-    <hyperlink ref="A574" r:id="rId507318"/>
-    <hyperlink ref="A575" r:id="rId507319"/>
-    <hyperlink ref="A576" r:id="rId507320"/>
-    <hyperlink ref="A577" r:id="rId507321"/>
-    <hyperlink ref="A578" r:id="rId507322"/>
-    <hyperlink ref="A579" r:id="rId507323"/>
-    <hyperlink ref="A580" r:id="rId507324"/>
-    <hyperlink ref="A581" r:id="rId507325"/>
-    <hyperlink ref="A582" r:id="rId507326"/>
-    <hyperlink ref="A583" r:id="rId507327"/>
-    <hyperlink ref="A584" r:id="rId507328"/>
-    <hyperlink ref="A585" r:id="rId507329"/>
-    <hyperlink ref="A586" r:id="rId507330"/>
-    <hyperlink ref="A587" r:id="rId507331"/>
-    <hyperlink ref="A588" r:id="rId507332"/>
-    <hyperlink ref="A589" r:id="rId507333"/>
-    <hyperlink ref="A590" r:id="rId507334"/>
-    <hyperlink ref="A591" r:id="rId507335"/>
-    <hyperlink ref="A592" r:id="rId507336"/>
-    <hyperlink ref="A593" r:id="rId507337"/>
-    <hyperlink ref="A594" r:id="rId507338"/>
-    <hyperlink ref="A595" r:id="rId507339"/>
-    <hyperlink ref="A596" r:id="rId507340"/>
-    <hyperlink ref="A597" r:id="rId507341"/>
-    <hyperlink ref="A598" r:id="rId507342"/>
-    <hyperlink ref="A599" r:id="rId507343"/>
-    <hyperlink ref="A600" r:id="rId507344"/>
-    <hyperlink ref="A601" r:id="rId507345"/>
-    <hyperlink ref="A602" r:id="rId507346"/>
-    <hyperlink ref="A603" r:id="rId507347"/>
-    <hyperlink ref="A604" r:id="rId507348"/>
-    <hyperlink ref="A605" r:id="rId507349"/>
-    <hyperlink ref="A606" r:id="rId507350"/>
-    <hyperlink ref="A607" r:id="rId507351"/>
-    <hyperlink ref="A608" r:id="rId507352"/>
-    <hyperlink ref="A609" r:id="rId507353"/>
-    <hyperlink ref="A610" r:id="rId507354"/>
-    <hyperlink ref="A611" r:id="rId507355"/>
-    <hyperlink ref="A612" r:id="rId507356"/>
-    <hyperlink ref="A613" r:id="rId507357"/>
-    <hyperlink ref="A614" r:id="rId507358"/>
-    <hyperlink ref="A615" r:id="rId507359"/>
-    <hyperlink ref="A616" r:id="rId507360"/>
-    <hyperlink ref="A617" r:id="rId507361"/>
-    <hyperlink ref="A618" r:id="rId507362"/>
-    <hyperlink ref="A619" r:id="rId507363"/>
-    <hyperlink ref="A620" r:id="rId507364"/>
-    <hyperlink ref="A621" r:id="rId507365"/>
-    <hyperlink ref="A622" r:id="rId507366"/>
-    <hyperlink ref="A623" r:id="rId507367"/>
-    <hyperlink ref="A624" r:id="rId507368"/>
-    <hyperlink ref="A625" r:id="rId507369"/>
-    <hyperlink ref="A626" r:id="rId507370"/>
-    <hyperlink ref="A627" r:id="rId507371"/>
-    <hyperlink ref="A628" r:id="rId507372"/>
-    <hyperlink ref="A629" r:id="rId507373"/>
-    <hyperlink ref="A630" r:id="rId507374"/>
-    <hyperlink ref="A631" r:id="rId507375"/>
-    <hyperlink ref="A632" r:id="rId507376"/>
+    <hyperlink ref="A7" r:id="rId471221"/>
+    <hyperlink ref="A8" r:id="rId471222"/>
+    <hyperlink ref="A9" r:id="rId471223"/>
+    <hyperlink ref="A10" r:id="rId471224"/>
+    <hyperlink ref="A11" r:id="rId471225"/>
+    <hyperlink ref="A12" r:id="rId471226"/>
+    <hyperlink ref="A13" r:id="rId471227"/>
+    <hyperlink ref="A14" r:id="rId471228"/>
+    <hyperlink ref="A15" r:id="rId471229"/>
+    <hyperlink ref="A16" r:id="rId471230"/>
+    <hyperlink ref="A17" r:id="rId471231"/>
+    <hyperlink ref="A18" r:id="rId471232"/>
+    <hyperlink ref="A19" r:id="rId471233"/>
+    <hyperlink ref="A20" r:id="rId471234"/>
+    <hyperlink ref="A21" r:id="rId471235"/>
+    <hyperlink ref="A22" r:id="rId471236"/>
+    <hyperlink ref="A23" r:id="rId471237"/>
+    <hyperlink ref="A24" r:id="rId471238"/>
+    <hyperlink ref="A25" r:id="rId471239"/>
+    <hyperlink ref="A26" r:id="rId471240"/>
+    <hyperlink ref="A27" r:id="rId471241"/>
+    <hyperlink ref="A28" r:id="rId471242"/>
+    <hyperlink ref="A29" r:id="rId471243"/>
+    <hyperlink ref="A30" r:id="rId471244"/>
+    <hyperlink ref="A31" r:id="rId471245"/>
+    <hyperlink ref="A32" r:id="rId471246"/>
+    <hyperlink ref="A33" r:id="rId471247"/>
+    <hyperlink ref="A34" r:id="rId471248"/>
+    <hyperlink ref="A35" r:id="rId471249"/>
+    <hyperlink ref="A36" r:id="rId471250"/>
+    <hyperlink ref="A37" r:id="rId471251"/>
+    <hyperlink ref="A38" r:id="rId471252"/>
+    <hyperlink ref="A39" r:id="rId471253"/>
+    <hyperlink ref="A40" r:id="rId471254"/>
+    <hyperlink ref="A41" r:id="rId471255"/>
+    <hyperlink ref="A42" r:id="rId471256"/>
+    <hyperlink ref="A43" r:id="rId471257"/>
+    <hyperlink ref="A44" r:id="rId471258"/>
+    <hyperlink ref="A45" r:id="rId471259"/>
+    <hyperlink ref="A46" r:id="rId471260"/>
+    <hyperlink ref="A47" r:id="rId471261"/>
+    <hyperlink ref="A48" r:id="rId471262"/>
+    <hyperlink ref="A49" r:id="rId471263"/>
+    <hyperlink ref="A50" r:id="rId471264"/>
+    <hyperlink ref="A51" r:id="rId471265"/>
+    <hyperlink ref="A52" r:id="rId471266"/>
+    <hyperlink ref="A53" r:id="rId471267"/>
+    <hyperlink ref="A54" r:id="rId471268"/>
+    <hyperlink ref="A55" r:id="rId471269"/>
+    <hyperlink ref="A56" r:id="rId471270"/>
+    <hyperlink ref="A57" r:id="rId471271"/>
+    <hyperlink ref="A58" r:id="rId471272"/>
+    <hyperlink ref="A59" r:id="rId471273"/>
+    <hyperlink ref="A60" r:id="rId471274"/>
+    <hyperlink ref="A61" r:id="rId471275"/>
+    <hyperlink ref="A62" r:id="rId471276"/>
+    <hyperlink ref="A63" r:id="rId471277"/>
+    <hyperlink ref="A64" r:id="rId471278"/>
+    <hyperlink ref="A65" r:id="rId471279"/>
+    <hyperlink ref="A66" r:id="rId471280"/>
+    <hyperlink ref="A67" r:id="rId471281"/>
+    <hyperlink ref="A68" r:id="rId471282"/>
+    <hyperlink ref="A69" r:id="rId471283"/>
+    <hyperlink ref="A70" r:id="rId471284"/>
+    <hyperlink ref="A71" r:id="rId471285"/>
+    <hyperlink ref="A72" r:id="rId471286"/>
+    <hyperlink ref="A73" r:id="rId471287"/>
+    <hyperlink ref="A74" r:id="rId471288"/>
+    <hyperlink ref="A75" r:id="rId471289"/>
+    <hyperlink ref="A76" r:id="rId471290"/>
+    <hyperlink ref="A77" r:id="rId471291"/>
+    <hyperlink ref="A78" r:id="rId471292"/>
+    <hyperlink ref="A79" r:id="rId471293"/>
+    <hyperlink ref="A80" r:id="rId471294"/>
+    <hyperlink ref="A81" r:id="rId471295"/>
+    <hyperlink ref="A82" r:id="rId471296"/>
+    <hyperlink ref="A83" r:id="rId471297"/>
+    <hyperlink ref="A84" r:id="rId471298"/>
+    <hyperlink ref="A85" r:id="rId471299"/>
+    <hyperlink ref="A86" r:id="rId471300"/>
+    <hyperlink ref="A87" r:id="rId471301"/>
+    <hyperlink ref="A88" r:id="rId471302"/>
+    <hyperlink ref="A89" r:id="rId471303"/>
+    <hyperlink ref="A90" r:id="rId471304"/>
+    <hyperlink ref="A91" r:id="rId471305"/>
+    <hyperlink ref="A92" r:id="rId471306"/>
+    <hyperlink ref="A93" r:id="rId471307"/>
+    <hyperlink ref="A94" r:id="rId471308"/>
+    <hyperlink ref="A95" r:id="rId471309"/>
+    <hyperlink ref="A96" r:id="rId471310"/>
+    <hyperlink ref="A97" r:id="rId471311"/>
+    <hyperlink ref="A98" r:id="rId471312"/>
+    <hyperlink ref="A99" r:id="rId471313"/>
+    <hyperlink ref="A100" r:id="rId471314"/>
+    <hyperlink ref="A101" r:id="rId471315"/>
+    <hyperlink ref="A102" r:id="rId471316"/>
+    <hyperlink ref="A103" r:id="rId471317"/>
+    <hyperlink ref="A104" r:id="rId471318"/>
+    <hyperlink ref="A105" r:id="rId471319"/>
+    <hyperlink ref="A106" r:id="rId471320"/>
+    <hyperlink ref="A107" r:id="rId471321"/>
+    <hyperlink ref="A108" r:id="rId471322"/>
+    <hyperlink ref="A109" r:id="rId471323"/>
+    <hyperlink ref="A110" r:id="rId471324"/>
+    <hyperlink ref="A111" r:id="rId471325"/>
+    <hyperlink ref="A112" r:id="rId471326"/>
+    <hyperlink ref="A113" r:id="rId471327"/>
+    <hyperlink ref="A114" r:id="rId471328"/>
+    <hyperlink ref="A115" r:id="rId471329"/>
+    <hyperlink ref="A116" r:id="rId471330"/>
+    <hyperlink ref="A117" r:id="rId471331"/>
+    <hyperlink ref="A118" r:id="rId471332"/>
+    <hyperlink ref="A119" r:id="rId471333"/>
+    <hyperlink ref="A120" r:id="rId471334"/>
+    <hyperlink ref="A121" r:id="rId471335"/>
+    <hyperlink ref="A122" r:id="rId471336"/>
+    <hyperlink ref="A123" r:id="rId471337"/>
+    <hyperlink ref="A124" r:id="rId471338"/>
+    <hyperlink ref="A125" r:id="rId471339"/>
+    <hyperlink ref="A126" r:id="rId471340"/>
+    <hyperlink ref="A127" r:id="rId471341"/>
+    <hyperlink ref="A128" r:id="rId471342"/>
+    <hyperlink ref="A129" r:id="rId471343"/>
+    <hyperlink ref="A130" r:id="rId471344"/>
+    <hyperlink ref="A131" r:id="rId471345"/>
+    <hyperlink ref="A132" r:id="rId471346"/>
+    <hyperlink ref="A133" r:id="rId471347"/>
+    <hyperlink ref="A134" r:id="rId471348"/>
+    <hyperlink ref="A135" r:id="rId471349"/>
+    <hyperlink ref="A136" r:id="rId471350"/>
+    <hyperlink ref="A137" r:id="rId471351"/>
+    <hyperlink ref="A138" r:id="rId471352"/>
+    <hyperlink ref="A139" r:id="rId471353"/>
+    <hyperlink ref="A140" r:id="rId471354"/>
+    <hyperlink ref="A141" r:id="rId471355"/>
+    <hyperlink ref="A142" r:id="rId471356"/>
+    <hyperlink ref="A143" r:id="rId471357"/>
+    <hyperlink ref="A144" r:id="rId471358"/>
+    <hyperlink ref="A145" r:id="rId471359"/>
+    <hyperlink ref="A146" r:id="rId471360"/>
+    <hyperlink ref="A147" r:id="rId471361"/>
+    <hyperlink ref="A148" r:id="rId471362"/>
+    <hyperlink ref="A149" r:id="rId471363"/>
+    <hyperlink ref="A150" r:id="rId471364"/>
+    <hyperlink ref="A151" r:id="rId471365"/>
+    <hyperlink ref="A152" r:id="rId471366"/>
+    <hyperlink ref="A153" r:id="rId471367"/>
+    <hyperlink ref="A154" r:id="rId471368"/>
+    <hyperlink ref="A155" r:id="rId471369"/>
+    <hyperlink ref="A156" r:id="rId471370"/>
+    <hyperlink ref="A157" r:id="rId471371"/>
+    <hyperlink ref="A158" r:id="rId471372"/>
+    <hyperlink ref="A159" r:id="rId471373"/>
+    <hyperlink ref="A160" r:id="rId471374"/>
+    <hyperlink ref="A161" r:id="rId471375"/>
+    <hyperlink ref="A162" r:id="rId471376"/>
+    <hyperlink ref="A163" r:id="rId471377"/>
+    <hyperlink ref="A164" r:id="rId471378"/>
+    <hyperlink ref="A165" r:id="rId471379"/>
+    <hyperlink ref="A166" r:id="rId471380"/>
+    <hyperlink ref="A167" r:id="rId471381"/>
+    <hyperlink ref="A168" r:id="rId471382"/>
+    <hyperlink ref="A169" r:id="rId471383"/>
+    <hyperlink ref="A170" r:id="rId471384"/>
+    <hyperlink ref="A171" r:id="rId471385"/>
+    <hyperlink ref="A172" r:id="rId471386"/>
+    <hyperlink ref="A173" r:id="rId471387"/>
+    <hyperlink ref="A174" r:id="rId471388"/>
+    <hyperlink ref="A175" r:id="rId471389"/>
+    <hyperlink ref="A176" r:id="rId471390"/>
+    <hyperlink ref="A177" r:id="rId471391"/>
+    <hyperlink ref="A178" r:id="rId471392"/>
+    <hyperlink ref="A179" r:id="rId471393"/>
+    <hyperlink ref="A180" r:id="rId471394"/>
+    <hyperlink ref="A181" r:id="rId471395"/>
+    <hyperlink ref="A182" r:id="rId471396"/>
+    <hyperlink ref="A183" r:id="rId471397"/>
+    <hyperlink ref="A184" r:id="rId471398"/>
+    <hyperlink ref="A185" r:id="rId471399"/>
+    <hyperlink ref="A186" r:id="rId471400"/>
+    <hyperlink ref="A187" r:id="rId471401"/>
+    <hyperlink ref="A188" r:id="rId471402"/>
+    <hyperlink ref="A189" r:id="rId471403"/>
+    <hyperlink ref="A190" r:id="rId471404"/>
+    <hyperlink ref="A191" r:id="rId471405"/>
+    <hyperlink ref="A192" r:id="rId471406"/>
+    <hyperlink ref="A193" r:id="rId471407"/>
+    <hyperlink ref="A194" r:id="rId471408"/>
+    <hyperlink ref="A195" r:id="rId471409"/>
+    <hyperlink ref="A196" r:id="rId471410"/>
+    <hyperlink ref="A197" r:id="rId471411"/>
+    <hyperlink ref="A198" r:id="rId471412"/>
+    <hyperlink ref="A199" r:id="rId471413"/>
+    <hyperlink ref="A200" r:id="rId471414"/>
+    <hyperlink ref="A201" r:id="rId471415"/>
+    <hyperlink ref="A202" r:id="rId471416"/>
+    <hyperlink ref="A203" r:id="rId471417"/>
+    <hyperlink ref="A204" r:id="rId471418"/>
+    <hyperlink ref="A205" r:id="rId471419"/>
+    <hyperlink ref="A206" r:id="rId471420"/>
+    <hyperlink ref="A207" r:id="rId471421"/>
+    <hyperlink ref="A208" r:id="rId471422"/>
+    <hyperlink ref="A209" r:id="rId471423"/>
+    <hyperlink ref="A210" r:id="rId471424"/>
+    <hyperlink ref="A211" r:id="rId471425"/>
+    <hyperlink ref="A212" r:id="rId471426"/>
+    <hyperlink ref="A213" r:id="rId471427"/>
+    <hyperlink ref="A214" r:id="rId471428"/>
+    <hyperlink ref="A215" r:id="rId471429"/>
+    <hyperlink ref="A216" r:id="rId471430"/>
+    <hyperlink ref="A217" r:id="rId471431"/>
+    <hyperlink ref="A218" r:id="rId471432"/>
+    <hyperlink ref="A219" r:id="rId471433"/>
+    <hyperlink ref="A220" r:id="rId471434"/>
+    <hyperlink ref="A221" r:id="rId471435"/>
+    <hyperlink ref="A222" r:id="rId471436"/>
+    <hyperlink ref="A223" r:id="rId471437"/>
+    <hyperlink ref="A224" r:id="rId471438"/>
+    <hyperlink ref="A225" r:id="rId471439"/>
+    <hyperlink ref="A226" r:id="rId471440"/>
+    <hyperlink ref="A227" r:id="rId471441"/>
+    <hyperlink ref="A228" r:id="rId471442"/>
+    <hyperlink ref="A229" r:id="rId471443"/>
+    <hyperlink ref="A230" r:id="rId471444"/>
+    <hyperlink ref="A231" r:id="rId471445"/>
+    <hyperlink ref="A232" r:id="rId471446"/>
+    <hyperlink ref="A233" r:id="rId471447"/>
+    <hyperlink ref="A234" r:id="rId471448"/>
+    <hyperlink ref="A235" r:id="rId471449"/>
+    <hyperlink ref="A236" r:id="rId471450"/>
+    <hyperlink ref="A237" r:id="rId471451"/>
+    <hyperlink ref="A238" r:id="rId471452"/>
+    <hyperlink ref="A239" r:id="rId471453"/>
+    <hyperlink ref="A240" r:id="rId471454"/>
+    <hyperlink ref="A241" r:id="rId471455"/>
+    <hyperlink ref="A242" r:id="rId471456"/>
+    <hyperlink ref="A243" r:id="rId471457"/>
+    <hyperlink ref="A244" r:id="rId471458"/>
+    <hyperlink ref="A245" r:id="rId471459"/>
+    <hyperlink ref="A246" r:id="rId471460"/>
+    <hyperlink ref="A247" r:id="rId471461"/>
+    <hyperlink ref="A248" r:id="rId471462"/>
+    <hyperlink ref="A249" r:id="rId471463"/>
+    <hyperlink ref="A250" r:id="rId471464"/>
+    <hyperlink ref="A251" r:id="rId471465"/>
+    <hyperlink ref="A252" r:id="rId471466"/>
+    <hyperlink ref="A253" r:id="rId471467"/>
+    <hyperlink ref="A254" r:id="rId471468"/>
+    <hyperlink ref="A255" r:id="rId471469"/>
+    <hyperlink ref="A256" r:id="rId471470"/>
+    <hyperlink ref="A257" r:id="rId471471"/>
+    <hyperlink ref="A258" r:id="rId471472"/>
+    <hyperlink ref="A259" r:id="rId471473"/>
+    <hyperlink ref="A260" r:id="rId471474"/>
+    <hyperlink ref="A261" r:id="rId471475"/>
+    <hyperlink ref="A262" r:id="rId471476"/>
+    <hyperlink ref="A263" r:id="rId471477"/>
+    <hyperlink ref="A264" r:id="rId471478"/>
+    <hyperlink ref="A265" r:id="rId471479"/>
+    <hyperlink ref="A266" r:id="rId471480"/>
+    <hyperlink ref="A267" r:id="rId471481"/>
+    <hyperlink ref="A268" r:id="rId471482"/>
+    <hyperlink ref="A269" r:id="rId471483"/>
+    <hyperlink ref="A270" r:id="rId471484"/>
+    <hyperlink ref="A271" r:id="rId471485"/>
+    <hyperlink ref="A272" r:id="rId471486"/>
+    <hyperlink ref="A273" r:id="rId471487"/>
+    <hyperlink ref="A274" r:id="rId471488"/>
+    <hyperlink ref="A275" r:id="rId471489"/>
+    <hyperlink ref="A276" r:id="rId471490"/>
+    <hyperlink ref="A277" r:id="rId471491"/>
+    <hyperlink ref="A278" r:id="rId471492"/>
+    <hyperlink ref="A279" r:id="rId471493"/>
+    <hyperlink ref="A280" r:id="rId471494"/>
+    <hyperlink ref="A281" r:id="rId471495"/>
+    <hyperlink ref="A282" r:id="rId471496"/>
+    <hyperlink ref="A283" r:id="rId471497"/>
+    <hyperlink ref="A284" r:id="rId471498"/>
+    <hyperlink ref="A285" r:id="rId471499"/>
+    <hyperlink ref="A286" r:id="rId471500"/>
+    <hyperlink ref="A287" r:id="rId471501"/>
+    <hyperlink ref="A288" r:id="rId471502"/>
+    <hyperlink ref="A289" r:id="rId471503"/>
+    <hyperlink ref="A290" r:id="rId471504"/>
+    <hyperlink ref="A291" r:id="rId471505"/>
+    <hyperlink ref="A292" r:id="rId471506"/>
+    <hyperlink ref="A293" r:id="rId471507"/>
+    <hyperlink ref="A294" r:id="rId471508"/>
+    <hyperlink ref="A295" r:id="rId471509"/>
+    <hyperlink ref="A296" r:id="rId471510"/>
+    <hyperlink ref="A297" r:id="rId471511"/>
+    <hyperlink ref="A298" r:id="rId471512"/>
+    <hyperlink ref="A299" r:id="rId471513"/>
+    <hyperlink ref="A300" r:id="rId471514"/>
+    <hyperlink ref="A301" r:id="rId471515"/>
+    <hyperlink ref="A302" r:id="rId471516"/>
+    <hyperlink ref="A303" r:id="rId471517"/>
+    <hyperlink ref="A304" r:id="rId471518"/>
+    <hyperlink ref="A305" r:id="rId471519"/>
+    <hyperlink ref="A306" r:id="rId471520"/>
+    <hyperlink ref="A307" r:id="rId471521"/>
+    <hyperlink ref="A308" r:id="rId471522"/>
+    <hyperlink ref="A309" r:id="rId471523"/>
+    <hyperlink ref="A310" r:id="rId471524"/>
+    <hyperlink ref="A311" r:id="rId471525"/>
+    <hyperlink ref="A312" r:id="rId471526"/>
+    <hyperlink ref="A313" r:id="rId471527"/>
+    <hyperlink ref="A314" r:id="rId471528"/>
+    <hyperlink ref="A315" r:id="rId471529"/>
+    <hyperlink ref="A316" r:id="rId471530"/>
+    <hyperlink ref="A317" r:id="rId471531"/>
+    <hyperlink ref="A318" r:id="rId471532"/>
+    <hyperlink ref="A319" r:id="rId471533"/>
+    <hyperlink ref="A320" r:id="rId471534"/>
+    <hyperlink ref="A321" r:id="rId471535"/>
+    <hyperlink ref="A322" r:id="rId471536"/>
+    <hyperlink ref="A323" r:id="rId471537"/>
+    <hyperlink ref="A324" r:id="rId471538"/>
+    <hyperlink ref="A325" r:id="rId471539"/>
+    <hyperlink ref="A326" r:id="rId471540"/>
+    <hyperlink ref="A327" r:id="rId471541"/>
+    <hyperlink ref="A328" r:id="rId471542"/>
+    <hyperlink ref="A329" r:id="rId471543"/>
+    <hyperlink ref="A330" r:id="rId471544"/>
+    <hyperlink ref="A331" r:id="rId471545"/>
+    <hyperlink ref="A332" r:id="rId471546"/>
+    <hyperlink ref="A333" r:id="rId471547"/>
+    <hyperlink ref="A334" r:id="rId471548"/>
+    <hyperlink ref="A335" r:id="rId471549"/>
+    <hyperlink ref="A336" r:id="rId471550"/>
+    <hyperlink ref="A337" r:id="rId471551"/>
+    <hyperlink ref="A338" r:id="rId471552"/>
+    <hyperlink ref="A339" r:id="rId471553"/>
+    <hyperlink ref="A340" r:id="rId471554"/>
+    <hyperlink ref="A341" r:id="rId471555"/>
+    <hyperlink ref="A342" r:id="rId471556"/>
+    <hyperlink ref="A343" r:id="rId471557"/>
+    <hyperlink ref="A344" r:id="rId471558"/>
+    <hyperlink ref="A345" r:id="rId471559"/>
+    <hyperlink ref="A346" r:id="rId471560"/>
+    <hyperlink ref="A347" r:id="rId471561"/>
+    <hyperlink ref="A348" r:id="rId471562"/>
+    <hyperlink ref="A349" r:id="rId471563"/>
+    <hyperlink ref="A350" r:id="rId471564"/>
+    <hyperlink ref="A351" r:id="rId471565"/>
+    <hyperlink ref="A352" r:id="rId471566"/>
+    <hyperlink ref="A353" r:id="rId471567"/>
+    <hyperlink ref="A354" r:id="rId471568"/>
+    <hyperlink ref="A355" r:id="rId471569"/>
+    <hyperlink ref="A356" r:id="rId471570"/>
+    <hyperlink ref="A357" r:id="rId471571"/>
+    <hyperlink ref="A358" r:id="rId471572"/>
+    <hyperlink ref="A359" r:id="rId471573"/>
+    <hyperlink ref="A360" r:id="rId471574"/>
+    <hyperlink ref="A361" r:id="rId471575"/>
+    <hyperlink ref="A362" r:id="rId471576"/>
+    <hyperlink ref="A363" r:id="rId471577"/>
+    <hyperlink ref="A364" r:id="rId471578"/>
+    <hyperlink ref="A365" r:id="rId471579"/>
+    <hyperlink ref="A366" r:id="rId471580"/>
+    <hyperlink ref="A367" r:id="rId471581"/>
+    <hyperlink ref="A368" r:id="rId471582"/>
+    <hyperlink ref="A369" r:id="rId471583"/>
+    <hyperlink ref="A370" r:id="rId471584"/>
+    <hyperlink ref="A371" r:id="rId471585"/>
+    <hyperlink ref="A372" r:id="rId471586"/>
+    <hyperlink ref="A373" r:id="rId471587"/>
+    <hyperlink ref="A374" r:id="rId471588"/>
+    <hyperlink ref="A375" r:id="rId471589"/>
+    <hyperlink ref="A376" r:id="rId471590"/>
+    <hyperlink ref="A377" r:id="rId471591"/>
+    <hyperlink ref="A378" r:id="rId471592"/>
+    <hyperlink ref="A379" r:id="rId471593"/>
+    <hyperlink ref="A380" r:id="rId471594"/>
+    <hyperlink ref="A381" r:id="rId471595"/>
+    <hyperlink ref="A382" r:id="rId471596"/>
+    <hyperlink ref="A383" r:id="rId471597"/>
+    <hyperlink ref="A384" r:id="rId471598"/>
+    <hyperlink ref="A385" r:id="rId471599"/>
+    <hyperlink ref="A386" r:id="rId471600"/>
+    <hyperlink ref="A387" r:id="rId471601"/>
+    <hyperlink ref="A388" r:id="rId471602"/>
+    <hyperlink ref="A389" r:id="rId471603"/>
+    <hyperlink ref="A390" r:id="rId471604"/>
+    <hyperlink ref="A391" r:id="rId471605"/>
+    <hyperlink ref="A392" r:id="rId471606"/>
+    <hyperlink ref="A393" r:id="rId471607"/>
+    <hyperlink ref="A394" r:id="rId471608"/>
+    <hyperlink ref="A395" r:id="rId471609"/>
+    <hyperlink ref="A396" r:id="rId471610"/>
+    <hyperlink ref="A397" r:id="rId471611"/>
+    <hyperlink ref="A398" r:id="rId471612"/>
+    <hyperlink ref="A399" r:id="rId471613"/>
+    <hyperlink ref="A400" r:id="rId471614"/>
+    <hyperlink ref="A401" r:id="rId471615"/>
+    <hyperlink ref="A402" r:id="rId471616"/>
+    <hyperlink ref="A403" r:id="rId471617"/>
+    <hyperlink ref="A404" r:id="rId471618"/>
+    <hyperlink ref="A405" r:id="rId471619"/>
+    <hyperlink ref="A406" r:id="rId471620"/>
+    <hyperlink ref="A407" r:id="rId471621"/>
+    <hyperlink ref="A408" r:id="rId471622"/>
+    <hyperlink ref="A409" r:id="rId471623"/>
+    <hyperlink ref="A410" r:id="rId471624"/>
+    <hyperlink ref="A411" r:id="rId471625"/>
+    <hyperlink ref="A412" r:id="rId471626"/>
+    <hyperlink ref="A413" r:id="rId471627"/>
+    <hyperlink ref="A414" r:id="rId471628"/>
+    <hyperlink ref="A415" r:id="rId471629"/>
+    <hyperlink ref="A416" r:id="rId471630"/>
+    <hyperlink ref="A417" r:id="rId471631"/>
+    <hyperlink ref="A418" r:id="rId471632"/>
+    <hyperlink ref="A419" r:id="rId471633"/>
+    <hyperlink ref="A420" r:id="rId471634"/>
+    <hyperlink ref="A421" r:id="rId471635"/>
+    <hyperlink ref="A422" r:id="rId471636"/>
+    <hyperlink ref="A423" r:id="rId471637"/>
+    <hyperlink ref="A424" r:id="rId471638"/>
+    <hyperlink ref="A425" r:id="rId471639"/>
+    <hyperlink ref="A426" r:id="rId471640"/>
+    <hyperlink ref="A427" r:id="rId471641"/>
+    <hyperlink ref="A428" r:id="rId471642"/>
+    <hyperlink ref="A429" r:id="rId471643"/>
+    <hyperlink ref="A430" r:id="rId471644"/>
+    <hyperlink ref="A431" r:id="rId471645"/>
+    <hyperlink ref="A432" r:id="rId471646"/>
+    <hyperlink ref="A433" r:id="rId471647"/>
+    <hyperlink ref="A434" r:id="rId471648"/>
+    <hyperlink ref="A435" r:id="rId471649"/>
+    <hyperlink ref="A436" r:id="rId471650"/>
+    <hyperlink ref="A437" r:id="rId471651"/>
+    <hyperlink ref="A438" r:id="rId471652"/>
+    <hyperlink ref="A439" r:id="rId471653"/>
+    <hyperlink ref="A440" r:id="rId471654"/>
+    <hyperlink ref="A441" r:id="rId471655"/>
+    <hyperlink ref="A442" r:id="rId471656"/>
+    <hyperlink ref="A443" r:id="rId471657"/>
+    <hyperlink ref="A444" r:id="rId471658"/>
+    <hyperlink ref="A445" r:id="rId471659"/>
+    <hyperlink ref="A446" r:id="rId471660"/>
+    <hyperlink ref="A447" r:id="rId471661"/>
+    <hyperlink ref="A448" r:id="rId471662"/>
+    <hyperlink ref="A449" r:id="rId471663"/>
+    <hyperlink ref="A450" r:id="rId471664"/>
+    <hyperlink ref="A451" r:id="rId471665"/>
+    <hyperlink ref="A452" r:id="rId471666"/>
+    <hyperlink ref="A453" r:id="rId471667"/>
+    <hyperlink ref="A454" r:id="rId471668"/>
+    <hyperlink ref="A455" r:id="rId471669"/>
+    <hyperlink ref="A456" r:id="rId471670"/>
+    <hyperlink ref="A457" r:id="rId471671"/>
+    <hyperlink ref="A458" r:id="rId471672"/>
+    <hyperlink ref="A459" r:id="rId471673"/>
+    <hyperlink ref="A460" r:id="rId471674"/>
+    <hyperlink ref="A461" r:id="rId471675"/>
+    <hyperlink ref="A462" r:id="rId471676"/>
+    <hyperlink ref="A463" r:id="rId471677"/>
+    <hyperlink ref="A464" r:id="rId471678"/>
+    <hyperlink ref="A465" r:id="rId471679"/>
+    <hyperlink ref="A466" r:id="rId471680"/>
+    <hyperlink ref="A467" r:id="rId471681"/>
+    <hyperlink ref="A468" r:id="rId471682"/>
+    <hyperlink ref="A469" r:id="rId471683"/>
+    <hyperlink ref="A470" r:id="rId471684"/>
+    <hyperlink ref="A471" r:id="rId471685"/>
+    <hyperlink ref="A472" r:id="rId471686"/>
+    <hyperlink ref="A473" r:id="rId471687"/>
+    <hyperlink ref="A474" r:id="rId471688"/>
+    <hyperlink ref="A475" r:id="rId471689"/>
+    <hyperlink ref="A476" r:id="rId471690"/>
+    <hyperlink ref="A477" r:id="rId471691"/>
+    <hyperlink ref="A478" r:id="rId471692"/>
+    <hyperlink ref="A479" r:id="rId471693"/>
+    <hyperlink ref="A480" r:id="rId471694"/>
+    <hyperlink ref="A481" r:id="rId471695"/>
+    <hyperlink ref="A482" r:id="rId471696"/>
+    <hyperlink ref="A483" r:id="rId471697"/>
+    <hyperlink ref="A484" r:id="rId471698"/>
+    <hyperlink ref="A485" r:id="rId471699"/>
+    <hyperlink ref="A486" r:id="rId471700"/>
+    <hyperlink ref="A487" r:id="rId471701"/>
+    <hyperlink ref="A488" r:id="rId471702"/>
+    <hyperlink ref="A489" r:id="rId471703"/>
+    <hyperlink ref="A490" r:id="rId471704"/>
+    <hyperlink ref="A491" r:id="rId471705"/>
+    <hyperlink ref="A492" r:id="rId471706"/>
+    <hyperlink ref="A493" r:id="rId471707"/>
+    <hyperlink ref="A494" r:id="rId471708"/>
+    <hyperlink ref="A495" r:id="rId471709"/>
+    <hyperlink ref="A496" r:id="rId471710"/>
+    <hyperlink ref="A497" r:id="rId471711"/>
+    <hyperlink ref="A498" r:id="rId471712"/>
+    <hyperlink ref="A499" r:id="rId471713"/>
+    <hyperlink ref="A500" r:id="rId471714"/>
+    <hyperlink ref="A501" r:id="rId471715"/>
+    <hyperlink ref="A502" r:id="rId471716"/>
+    <hyperlink ref="A503" r:id="rId471717"/>
+    <hyperlink ref="A504" r:id="rId471718"/>
+    <hyperlink ref="A505" r:id="rId471719"/>
+    <hyperlink ref="A506" r:id="rId471720"/>
+    <hyperlink ref="A507" r:id="rId471721"/>
+    <hyperlink ref="A508" r:id="rId471722"/>
+    <hyperlink ref="A509" r:id="rId471723"/>
+    <hyperlink ref="A510" r:id="rId471724"/>
+    <hyperlink ref="A511" r:id="rId471725"/>
+    <hyperlink ref="A512" r:id="rId471726"/>
+    <hyperlink ref="A513" r:id="rId471727"/>
+    <hyperlink ref="A514" r:id="rId471728"/>
+    <hyperlink ref="A515" r:id="rId471729"/>
+    <hyperlink ref="A516" r:id="rId471730"/>
+    <hyperlink ref="A517" r:id="rId471731"/>
+    <hyperlink ref="A518" r:id="rId471732"/>
+    <hyperlink ref="A519" r:id="rId471733"/>
+    <hyperlink ref="A520" r:id="rId471734"/>
+    <hyperlink ref="A521" r:id="rId471735"/>
+    <hyperlink ref="A522" r:id="rId471736"/>
+    <hyperlink ref="A523" r:id="rId471737"/>
+    <hyperlink ref="A524" r:id="rId471738"/>
+    <hyperlink ref="A525" r:id="rId471739"/>
+    <hyperlink ref="A526" r:id="rId471740"/>
+    <hyperlink ref="A527" r:id="rId471741"/>
+    <hyperlink ref="A528" r:id="rId471742"/>
+    <hyperlink ref="A529" r:id="rId471743"/>
+    <hyperlink ref="A530" r:id="rId471744"/>
+    <hyperlink ref="A531" r:id="rId471745"/>
+    <hyperlink ref="A532" r:id="rId471746"/>
+    <hyperlink ref="A533" r:id="rId471747"/>
+    <hyperlink ref="A534" r:id="rId471748"/>
+    <hyperlink ref="A535" r:id="rId471749"/>
+    <hyperlink ref="A536" r:id="rId471750"/>
+    <hyperlink ref="A537" r:id="rId471751"/>
+    <hyperlink ref="A538" r:id="rId471752"/>
+    <hyperlink ref="A539" r:id="rId471753"/>
+    <hyperlink ref="A540" r:id="rId471754"/>
+    <hyperlink ref="A541" r:id="rId471755"/>
+    <hyperlink ref="A542" r:id="rId471756"/>
+    <hyperlink ref="A543" r:id="rId471757"/>
+    <hyperlink ref="A544" r:id="rId471758"/>
+    <hyperlink ref="A545" r:id="rId471759"/>
+    <hyperlink ref="A546" r:id="rId471760"/>
+    <hyperlink ref="A547" r:id="rId471761"/>
+    <hyperlink ref="A548" r:id="rId471762"/>
+    <hyperlink ref="A549" r:id="rId471763"/>
+    <hyperlink ref="A550" r:id="rId471764"/>
+    <hyperlink ref="A551" r:id="rId471765"/>
+    <hyperlink ref="A552" r:id="rId471766"/>
+    <hyperlink ref="A553" r:id="rId471767"/>
+    <hyperlink ref="A554" r:id="rId471768"/>
+    <hyperlink ref="A555" r:id="rId471769"/>
+    <hyperlink ref="A556" r:id="rId471770"/>
+    <hyperlink ref="A557" r:id="rId471771"/>
+    <hyperlink ref="A558" r:id="rId471772"/>
+    <hyperlink ref="A559" r:id="rId471773"/>
+    <hyperlink ref="A560" r:id="rId471774"/>
+    <hyperlink ref="A561" r:id="rId471775"/>
+    <hyperlink ref="A562" r:id="rId471776"/>
+    <hyperlink ref="A563" r:id="rId471777"/>
+    <hyperlink ref="A564" r:id="rId471778"/>
+    <hyperlink ref="A565" r:id="rId471779"/>
+    <hyperlink ref="A566" r:id="rId471780"/>
+    <hyperlink ref="A567" r:id="rId471781"/>
+    <hyperlink ref="A568" r:id="rId471782"/>
+    <hyperlink ref="A569" r:id="rId471783"/>
+    <hyperlink ref="A570" r:id="rId471784"/>
+    <hyperlink ref="A571" r:id="rId471785"/>
+    <hyperlink ref="A572" r:id="rId471786"/>
+    <hyperlink ref="A573" r:id="rId471787"/>
+    <hyperlink ref="A574" r:id="rId471788"/>
+    <hyperlink ref="A575" r:id="rId471789"/>
+    <hyperlink ref="A576" r:id="rId471790"/>
+    <hyperlink ref="A577" r:id="rId471791"/>
+    <hyperlink ref="A578" r:id="rId471792"/>
+    <hyperlink ref="A579" r:id="rId471793"/>
+    <hyperlink ref="A580" r:id="rId471794"/>
+    <hyperlink ref="A581" r:id="rId471795"/>
+    <hyperlink ref="A582" r:id="rId471796"/>
+    <hyperlink ref="A583" r:id="rId471797"/>
+    <hyperlink ref="A584" r:id="rId471798"/>
+    <hyperlink ref="A585" r:id="rId471799"/>
+    <hyperlink ref="A586" r:id="rId471800"/>
+    <hyperlink ref="A587" r:id="rId471801"/>
+    <hyperlink ref="A588" r:id="rId471802"/>
+    <hyperlink ref="A589" r:id="rId471803"/>
+    <hyperlink ref="A590" r:id="rId471804"/>
+    <hyperlink ref="A591" r:id="rId471805"/>
+    <hyperlink ref="A592" r:id="rId471806"/>
+    <hyperlink ref="A593" r:id="rId471807"/>
+    <hyperlink ref="A594" r:id="rId471808"/>
+    <hyperlink ref="A595" r:id="rId471809"/>
+    <hyperlink ref="A596" r:id="rId471810"/>
+    <hyperlink ref="A597" r:id="rId471811"/>
+    <hyperlink ref="A598" r:id="rId471812"/>
+    <hyperlink ref="A599" r:id="rId471813"/>
+    <hyperlink ref="A600" r:id="rId471814"/>
+    <hyperlink ref="A601" r:id="rId471815"/>
+    <hyperlink ref="A602" r:id="rId471816"/>
+    <hyperlink ref="A603" r:id="rId471817"/>
+    <hyperlink ref="A604" r:id="rId471818"/>
+    <hyperlink ref="A605" r:id="rId471819"/>
+    <hyperlink ref="A606" r:id="rId471820"/>
+    <hyperlink ref="A607" r:id="rId471821"/>
+    <hyperlink ref="A608" r:id="rId471822"/>
+    <hyperlink ref="A609" r:id="rId471823"/>
+    <hyperlink ref="A610" r:id="rId471824"/>
+    <hyperlink ref="A611" r:id="rId471825"/>
+    <hyperlink ref="A612" r:id="rId471826"/>
+    <hyperlink ref="A613" r:id="rId471827"/>
+    <hyperlink ref="A614" r:id="rId471828"/>
+    <hyperlink ref="A615" r:id="rId471829"/>
+    <hyperlink ref="A616" r:id="rId471830"/>
+    <hyperlink ref="A617" r:id="rId471831"/>
+    <hyperlink ref="A618" r:id="rId471832"/>
+    <hyperlink ref="A619" r:id="rId471833"/>
+    <hyperlink ref="A620" r:id="rId471834"/>
+    <hyperlink ref="A621" r:id="rId471835"/>
+    <hyperlink ref="A622" r:id="rId471836"/>
+    <hyperlink ref="A623" r:id="rId471837"/>
+    <hyperlink ref="A624" r:id="rId471838"/>
+    <hyperlink ref="A625" r:id="rId471839"/>
+    <hyperlink ref="A626" r:id="rId471840"/>
+    <hyperlink ref="A627" r:id="rId471841"/>
+    <hyperlink ref="A628" r:id="rId471842"/>
+    <hyperlink ref="A629" r:id="rId471843"/>
+    <hyperlink ref="A630" r:id="rId471844"/>
+    <hyperlink ref="A631" r:id="rId471845"/>
+    <hyperlink ref="A632" r:id="rId471846"/>
   </hyperlinks>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter/>

--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -2066,13 +2066,9 @@
 ЧТОБЫ повысить производительность команды как запаздывающий показатель</t>
   </si>
   <si>
-    <t xml:space="preserve">Критерии успешности: рост Velocity Команды на (СРЕДНЕЕ НА 1 ШЕ) - 123% (без учета новых сотрудников)
-Формула: Ср. рост БА за 3Q на 1 ШЕ
-менее 0,75 = 0%
-[0,75 - 1) = 50%
-[1 - (1.XX - 5%)) = 75%
-[(1.XX - 5%) - (1.XX + 5%)] = 100%
-более (1.XX + 5%) = 125%</t>
+    <t xml:space="preserve">Рост производительности команды на 25%*
+352,8 -&gt; 470,2
+(без учета сотрудников, работающих первый полный квартал)</t>
   </si>
   <si>
     <t xml:space="preserve">#65914704</t>
@@ -4633,13 +4629,8 @@
 ЧТОБЫ повысить производительность команды как запаздывающий показатель</t>
   </si>
   <si>
-    <t xml:space="preserve">Критерии успешности: рост Velocity Команды на (СРЕДНЕЕ НА 1 ШЕ) = 50% 
-Формула: Ср. рост БА за 3Q на 1 ШЕ = 1.68 (67%)
-менее 0,75 = 0%
-[0,75 - 1) = 50%
-[1 - (1.50 - 5%)) = 75%
-[(1.50 - 5%) - (1.50 + 5%)] = 100%
-более (1.50 + 5%) = 125%</t>
+    <t xml:space="preserve">Рост производительности на 53%
+39,77 -&gt; 66,65  SP</t>
   </si>
   <si>
     <t xml:space="preserve">KPI_расчеты.xlsx ( 15K )</t>
@@ -27713,8 +27704,8 @@
 ЧТОБЫ повысить производительность команды как запаздывающий показатель</t>
   </si>
   <si>
-    <t xml:space="preserve">Рост производительности отдела 19 % 
-676-&gt; 709 SP</t>
+    <t xml:space="preserve">Рост производительности отдела 19,4 % 
+96-&gt; 101 SP</t>
   </si>
   <si>
     <t xml:space="preserve">#98464179</t>
@@ -30730,10 +30721,10 @@
         <v>619</v>
       </c>
       <c r="Q43" s="6">
-        <v>100.0000000000</v>
+        <v>125.0000000000</v>
       </c>
       <c r="R43" s="6">
-        <v>125.0000000000</v>
+        <v>136.0000000000</v>
       </c>
     </row>
     <row r="44">
@@ -33671,10 +33662,10 @@
         <v>1383</v>
       </c>
       <c r="Q99" s="6">
-        <v>100.0000000000</v>
+        <v>153.0000000000</v>
       </c>
       <c r="R99" s="6">
-        <v>125.0000000000</v>
+        <v>168.0000000000</v>
       </c>
       <c r="T99" s="1" t="s">
         <v>1384</v>
@@ -60530,632 +60521,632 @@
     <mergeCell ref="AG5:AG6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId471221"/>
-    <hyperlink ref="A8" r:id="rId471222"/>
-    <hyperlink ref="A9" r:id="rId471223"/>
-    <hyperlink ref="A10" r:id="rId471224"/>
-    <hyperlink ref="A11" r:id="rId471225"/>
-    <hyperlink ref="A12" r:id="rId471226"/>
-    <hyperlink ref="A13" r:id="rId471227"/>
-    <hyperlink ref="A14" r:id="rId471228"/>
-    <hyperlink ref="A15" r:id="rId471229"/>
-    <hyperlink ref="A16" r:id="rId471230"/>
-    <hyperlink ref="A17" r:id="rId471231"/>
-    <hyperlink ref="A18" r:id="rId471232"/>
-    <hyperlink ref="A19" r:id="rId471233"/>
-    <hyperlink ref="A20" r:id="rId471234"/>
-    <hyperlink ref="A21" r:id="rId471235"/>
-    <hyperlink ref="A22" r:id="rId471236"/>
-    <hyperlink ref="A23" r:id="rId471237"/>
-    <hyperlink ref="A24" r:id="rId471238"/>
-    <hyperlink ref="A25" r:id="rId471239"/>
-    <hyperlink ref="A26" r:id="rId471240"/>
-    <hyperlink ref="A27" r:id="rId471241"/>
-    <hyperlink ref="A28" r:id="rId471242"/>
-    <hyperlink ref="A29" r:id="rId471243"/>
-    <hyperlink ref="A30" r:id="rId471244"/>
-    <hyperlink ref="A31" r:id="rId471245"/>
-    <hyperlink ref="A32" r:id="rId471246"/>
-    <hyperlink ref="A33" r:id="rId471247"/>
-    <hyperlink ref="A34" r:id="rId471248"/>
-    <hyperlink ref="A35" r:id="rId471249"/>
-    <hyperlink ref="A36" r:id="rId471250"/>
-    <hyperlink ref="A37" r:id="rId471251"/>
-    <hyperlink ref="A38" r:id="rId471252"/>
-    <hyperlink ref="A39" r:id="rId471253"/>
-    <hyperlink ref="A40" r:id="rId471254"/>
-    <hyperlink ref="A41" r:id="rId471255"/>
-    <hyperlink ref="A42" r:id="rId471256"/>
-    <hyperlink ref="A43" r:id="rId471257"/>
-    <hyperlink ref="A44" r:id="rId471258"/>
-    <hyperlink ref="A45" r:id="rId471259"/>
-    <hyperlink ref="A46" r:id="rId471260"/>
-    <hyperlink ref="A47" r:id="rId471261"/>
-    <hyperlink ref="A48" r:id="rId471262"/>
-    <hyperlink ref="A49" r:id="rId471263"/>
-    <hyperlink ref="A50" r:id="rId471264"/>
-    <hyperlink ref="A51" r:id="rId471265"/>
-    <hyperlink ref="A52" r:id="rId471266"/>
-    <hyperlink ref="A53" r:id="rId471267"/>
-    <hyperlink ref="A54" r:id="rId471268"/>
-    <hyperlink ref="A55" r:id="rId471269"/>
-    <hyperlink ref="A56" r:id="rId471270"/>
-    <hyperlink ref="A57" r:id="rId471271"/>
-    <hyperlink ref="A58" r:id="rId471272"/>
-    <hyperlink ref="A59" r:id="rId471273"/>
-    <hyperlink ref="A60" r:id="rId471274"/>
-    <hyperlink ref="A61" r:id="rId471275"/>
-    <hyperlink ref="A62" r:id="rId471276"/>
-    <hyperlink ref="A63" r:id="rId471277"/>
-    <hyperlink ref="A64" r:id="rId471278"/>
-    <hyperlink ref="A65" r:id="rId471279"/>
-    <hyperlink ref="A66" r:id="rId471280"/>
-    <hyperlink ref="A67" r:id="rId471281"/>
-    <hyperlink ref="A68" r:id="rId471282"/>
-    <hyperlink ref="A69" r:id="rId471283"/>
-    <hyperlink ref="A70" r:id="rId471284"/>
-    <hyperlink ref="A71" r:id="rId471285"/>
-    <hyperlink ref="A72" r:id="rId471286"/>
-    <hyperlink ref="A73" r:id="rId471287"/>
-    <hyperlink ref="A74" r:id="rId471288"/>
-    <hyperlink ref="A75" r:id="rId471289"/>
-    <hyperlink ref="A76" r:id="rId471290"/>
-    <hyperlink ref="A77" r:id="rId471291"/>
-    <hyperlink ref="A78" r:id="rId471292"/>
-    <hyperlink ref="A79" r:id="rId471293"/>
-    <hyperlink ref="A80" r:id="rId471294"/>
-    <hyperlink ref="A81" r:id="rId471295"/>
-    <hyperlink ref="A82" r:id="rId471296"/>
-    <hyperlink ref="A83" r:id="rId471297"/>
-    <hyperlink ref="A84" r:id="rId471298"/>
-    <hyperlink ref="A85" r:id="rId471299"/>
-    <hyperlink ref="A86" r:id="rId471300"/>
-    <hyperlink ref="A87" r:id="rId471301"/>
-    <hyperlink ref="A88" r:id="rId471302"/>
-    <hyperlink ref="A89" r:id="rId471303"/>
-    <hyperlink ref="A90" r:id="rId471304"/>
-    <hyperlink ref="A91" r:id="rId471305"/>
-    <hyperlink ref="A92" r:id="rId471306"/>
-    <hyperlink ref="A93" r:id="rId471307"/>
-    <hyperlink ref="A94" r:id="rId471308"/>
-    <hyperlink ref="A95" r:id="rId471309"/>
-    <hyperlink ref="A96" r:id="rId471310"/>
-    <hyperlink ref="A97" r:id="rId471311"/>
-    <hyperlink ref="A98" r:id="rId471312"/>
-    <hyperlink ref="A99" r:id="rId471313"/>
-    <hyperlink ref="A100" r:id="rId471314"/>
-    <hyperlink ref="A101" r:id="rId471315"/>
-    <hyperlink ref="A102" r:id="rId471316"/>
-    <hyperlink ref="A103" r:id="rId471317"/>
-    <hyperlink ref="A104" r:id="rId471318"/>
-    <hyperlink ref="A105" r:id="rId471319"/>
-    <hyperlink ref="A106" r:id="rId471320"/>
-    <hyperlink ref="A107" r:id="rId471321"/>
-    <hyperlink ref="A108" r:id="rId471322"/>
-    <hyperlink ref="A109" r:id="rId471323"/>
-    <hyperlink ref="A110" r:id="rId471324"/>
-    <hyperlink ref="A111" r:id="rId471325"/>
-    <hyperlink ref="A112" r:id="rId471326"/>
-    <hyperlink ref="A113" r:id="rId471327"/>
-    <hyperlink ref="A114" r:id="rId471328"/>
-    <hyperlink ref="A115" r:id="rId471329"/>
-    <hyperlink ref="A116" r:id="rId471330"/>
-    <hyperlink ref="A117" r:id="rId471331"/>
-    <hyperlink ref="A118" r:id="rId471332"/>
-    <hyperlink ref="A119" r:id="rId471333"/>
-    <hyperlink ref="A120" r:id="rId471334"/>
-    <hyperlink ref="A121" r:id="rId471335"/>
-    <hyperlink ref="A122" r:id="rId471336"/>
-    <hyperlink ref="A123" r:id="rId471337"/>
-    <hyperlink ref="A124" r:id="rId471338"/>
-    <hyperlink ref="A125" r:id="rId471339"/>
-    <hyperlink ref="A126" r:id="rId471340"/>
-    <hyperlink ref="A127" r:id="rId471341"/>
-    <hyperlink ref="A128" r:id="rId471342"/>
-    <hyperlink ref="A129" r:id="rId471343"/>
-    <hyperlink ref="A130" r:id="rId471344"/>
-    <hyperlink ref="A131" r:id="rId471345"/>
-    <hyperlink ref="A132" r:id="rId471346"/>
-    <hyperlink ref="A133" r:id="rId471347"/>
-    <hyperlink ref="A134" r:id="rId471348"/>
-    <hyperlink ref="A135" r:id="rId471349"/>
-    <hyperlink ref="A136" r:id="rId471350"/>
-    <hyperlink ref="A137" r:id="rId471351"/>
-    <hyperlink ref="A138" r:id="rId471352"/>
-    <hyperlink ref="A139" r:id="rId471353"/>
-    <hyperlink ref="A140" r:id="rId471354"/>
-    <hyperlink ref="A141" r:id="rId471355"/>
-    <hyperlink ref="A142" r:id="rId471356"/>
-    <hyperlink ref="A143" r:id="rId471357"/>
-    <hyperlink ref="A144" r:id="rId471358"/>
-    <hyperlink ref="A145" r:id="rId471359"/>
-    <hyperlink ref="A146" r:id="rId471360"/>
-    <hyperlink ref="A147" r:id="rId471361"/>
-    <hyperlink ref="A148" r:id="rId471362"/>
-    <hyperlink ref="A149" r:id="rId471363"/>
-    <hyperlink ref="A150" r:id="rId471364"/>
-    <hyperlink ref="A151" r:id="rId471365"/>
-    <hyperlink ref="A152" r:id="rId471366"/>
-    <hyperlink ref="A153" r:id="rId471367"/>
-    <hyperlink ref="A154" r:id="rId471368"/>
-    <hyperlink ref="A155" r:id="rId471369"/>
-    <hyperlink ref="A156" r:id="rId471370"/>
-    <hyperlink ref="A157" r:id="rId471371"/>
-    <hyperlink ref="A158" r:id="rId471372"/>
-    <hyperlink ref="A159" r:id="rId471373"/>
-    <hyperlink ref="A160" r:id="rId471374"/>
-    <hyperlink ref="A161" r:id="rId471375"/>
-    <hyperlink ref="A162" r:id="rId471376"/>
-    <hyperlink ref="A163" r:id="rId471377"/>
-    <hyperlink ref="A164" r:id="rId471378"/>
-    <hyperlink ref="A165" r:id="rId471379"/>
-    <hyperlink ref="A166" r:id="rId471380"/>
-    <hyperlink ref="A167" r:id="rId471381"/>
-    <hyperlink ref="A168" r:id="rId471382"/>
-    <hyperlink ref="A169" r:id="rId471383"/>
-    <hyperlink ref="A170" r:id="rId471384"/>
-    <hyperlink ref="A171" r:id="rId471385"/>
-    <hyperlink ref="A172" r:id="rId471386"/>
-    <hyperlink ref="A173" r:id="rId471387"/>
-    <hyperlink ref="A174" r:id="rId471388"/>
-    <hyperlink ref="A175" r:id="rId471389"/>
-    <hyperlink ref="A176" r:id="rId471390"/>
-    <hyperlink ref="A177" r:id="rId471391"/>
-    <hyperlink ref="A178" r:id="rId471392"/>
-    <hyperlink ref="A179" r:id="rId471393"/>
-    <hyperlink ref="A180" r:id="rId471394"/>
-    <hyperlink ref="A181" r:id="rId471395"/>
-    <hyperlink ref="A182" r:id="rId471396"/>
-    <hyperlink ref="A183" r:id="rId471397"/>
-    <hyperlink ref="A184" r:id="rId471398"/>
-    <hyperlink ref="A185" r:id="rId471399"/>
-    <hyperlink ref="A186" r:id="rId471400"/>
-    <hyperlink ref="A187" r:id="rId471401"/>
-    <hyperlink ref="A188" r:id="rId471402"/>
-    <hyperlink ref="A189" r:id="rId471403"/>
-    <hyperlink ref="A190" r:id="rId471404"/>
-    <hyperlink ref="A191" r:id="rId471405"/>
-    <hyperlink ref="A192" r:id="rId471406"/>
-    <hyperlink ref="A193" r:id="rId471407"/>
-    <hyperlink ref="A194" r:id="rId471408"/>
-    <hyperlink ref="A195" r:id="rId471409"/>
-    <hyperlink ref="A196" r:id="rId471410"/>
-    <hyperlink ref="A197" r:id="rId471411"/>
-    <hyperlink ref="A198" r:id="rId471412"/>
-    <hyperlink ref="A199" r:id="rId471413"/>
-    <hyperlink ref="A200" r:id="rId471414"/>
-    <hyperlink ref="A201" r:id="rId471415"/>
-    <hyperlink ref="A202" r:id="rId471416"/>
-    <hyperlink ref="A203" r:id="rId471417"/>
-    <hyperlink ref="A204" r:id="rId471418"/>
-    <hyperlink ref="A205" r:id="rId471419"/>
-    <hyperlink ref="A206" r:id="rId471420"/>
-    <hyperlink ref="A207" r:id="rId471421"/>
-    <hyperlink ref="A208" r:id="rId471422"/>
-    <hyperlink ref="A209" r:id="rId471423"/>
-    <hyperlink ref="A210" r:id="rId471424"/>
-    <hyperlink ref="A211" r:id="rId471425"/>
-    <hyperlink ref="A212" r:id="rId471426"/>
-    <hyperlink ref="A213" r:id="rId471427"/>
-    <hyperlink ref="A214" r:id="rId471428"/>
-    <hyperlink ref="A215" r:id="rId471429"/>
-    <hyperlink ref="A216" r:id="rId471430"/>
-    <hyperlink ref="A217" r:id="rId471431"/>
-    <hyperlink ref="A218" r:id="rId471432"/>
-    <hyperlink ref="A219" r:id="rId471433"/>
-    <hyperlink ref="A220" r:id="rId471434"/>
-    <hyperlink ref="A221" r:id="rId471435"/>
-    <hyperlink ref="A222" r:id="rId471436"/>
-    <hyperlink ref="A223" r:id="rId471437"/>
-    <hyperlink ref="A224" r:id="rId471438"/>
-    <hyperlink ref="A225" r:id="rId471439"/>
-    <hyperlink ref="A226" r:id="rId471440"/>
-    <hyperlink ref="A227" r:id="rId471441"/>
-    <hyperlink ref="A228" r:id="rId471442"/>
-    <hyperlink ref="A229" r:id="rId471443"/>
-    <hyperlink ref="A230" r:id="rId471444"/>
-    <hyperlink ref="A231" r:id="rId471445"/>
-    <hyperlink ref="A232" r:id="rId471446"/>
-    <hyperlink ref="A233" r:id="rId471447"/>
-    <hyperlink ref="A234" r:id="rId471448"/>
-    <hyperlink ref="A235" r:id="rId471449"/>
-    <hyperlink ref="A236" r:id="rId471450"/>
-    <hyperlink ref="A237" r:id="rId471451"/>
-    <hyperlink ref="A238" r:id="rId471452"/>
-    <hyperlink ref="A239" r:id="rId471453"/>
-    <hyperlink ref="A240" r:id="rId471454"/>
-    <hyperlink ref="A241" r:id="rId471455"/>
-    <hyperlink ref="A242" r:id="rId471456"/>
-    <hyperlink ref="A243" r:id="rId471457"/>
-    <hyperlink ref="A244" r:id="rId471458"/>
-    <hyperlink ref="A245" r:id="rId471459"/>
-    <hyperlink ref="A246" r:id="rId471460"/>
-    <hyperlink ref="A247" r:id="rId471461"/>
-    <hyperlink ref="A248" r:id="rId471462"/>
-    <hyperlink ref="A249" r:id="rId471463"/>
-    <hyperlink ref="A250" r:id="rId471464"/>
-    <hyperlink ref="A251" r:id="rId471465"/>
-    <hyperlink ref="A252" r:id="rId471466"/>
-    <hyperlink ref="A253" r:id="rId471467"/>
-    <hyperlink ref="A254" r:id="rId471468"/>
-    <hyperlink ref="A255" r:id="rId471469"/>
-    <hyperlink ref="A256" r:id="rId471470"/>
-    <hyperlink ref="A257" r:id="rId471471"/>
-    <hyperlink ref="A258" r:id="rId471472"/>
-    <hyperlink ref="A259" r:id="rId471473"/>
-    <hyperlink ref="A260" r:id="rId471474"/>
-    <hyperlink ref="A261" r:id="rId471475"/>
-    <hyperlink ref="A262" r:id="rId471476"/>
-    <hyperlink ref="A263" r:id="rId471477"/>
-    <hyperlink ref="A264" r:id="rId471478"/>
-    <hyperlink ref="A265" r:id="rId471479"/>
-    <hyperlink ref="A266" r:id="rId471480"/>
-    <hyperlink ref="A267" r:id="rId471481"/>
-    <hyperlink ref="A268" r:id="rId471482"/>
-    <hyperlink ref="A269" r:id="rId471483"/>
-    <hyperlink ref="A270" r:id="rId471484"/>
-    <hyperlink ref="A271" r:id="rId471485"/>
-    <hyperlink ref="A272" r:id="rId471486"/>
-    <hyperlink ref="A273" r:id="rId471487"/>
-    <hyperlink ref="A274" r:id="rId471488"/>
-    <hyperlink ref="A275" r:id="rId471489"/>
-    <hyperlink ref="A276" r:id="rId471490"/>
-    <hyperlink ref="A277" r:id="rId471491"/>
-    <hyperlink ref="A278" r:id="rId471492"/>
-    <hyperlink ref="A279" r:id="rId471493"/>
-    <hyperlink ref="A280" r:id="rId471494"/>
-    <hyperlink ref="A281" r:id="rId471495"/>
-    <hyperlink ref="A282" r:id="rId471496"/>
-    <hyperlink ref="A283" r:id="rId471497"/>
-    <hyperlink ref="A284" r:id="rId471498"/>
-    <hyperlink ref="A285" r:id="rId471499"/>
-    <hyperlink ref="A286" r:id="rId471500"/>
-    <hyperlink ref="A287" r:id="rId471501"/>
-    <hyperlink ref="A288" r:id="rId471502"/>
-    <hyperlink ref="A289" r:id="rId471503"/>
-    <hyperlink ref="A290" r:id="rId471504"/>
-    <hyperlink ref="A291" r:id="rId471505"/>
-    <hyperlink ref="A292" r:id="rId471506"/>
-    <hyperlink ref="A293" r:id="rId471507"/>
-    <hyperlink ref="A294" r:id="rId471508"/>
-    <hyperlink ref="A295" r:id="rId471509"/>
-    <hyperlink ref="A296" r:id="rId471510"/>
-    <hyperlink ref="A297" r:id="rId471511"/>
-    <hyperlink ref="A298" r:id="rId471512"/>
-    <hyperlink ref="A299" r:id="rId471513"/>
-    <hyperlink ref="A300" r:id="rId471514"/>
-    <hyperlink ref="A301" r:id="rId471515"/>
-    <hyperlink ref="A302" r:id="rId471516"/>
-    <hyperlink ref="A303" r:id="rId471517"/>
-    <hyperlink ref="A304" r:id="rId471518"/>
-    <hyperlink ref="A305" r:id="rId471519"/>
-    <hyperlink ref="A306" r:id="rId471520"/>
-    <hyperlink ref="A307" r:id="rId471521"/>
-    <hyperlink ref="A308" r:id="rId471522"/>
-    <hyperlink ref="A309" r:id="rId471523"/>
-    <hyperlink ref="A310" r:id="rId471524"/>
-    <hyperlink ref="A311" r:id="rId471525"/>
-    <hyperlink ref="A312" r:id="rId471526"/>
-    <hyperlink ref="A313" r:id="rId471527"/>
-    <hyperlink ref="A314" r:id="rId471528"/>
-    <hyperlink ref="A315" r:id="rId471529"/>
-    <hyperlink ref="A316" r:id="rId471530"/>
-    <hyperlink ref="A317" r:id="rId471531"/>
-    <hyperlink ref="A318" r:id="rId471532"/>
-    <hyperlink ref="A319" r:id="rId471533"/>
-    <hyperlink ref="A320" r:id="rId471534"/>
-    <hyperlink ref="A321" r:id="rId471535"/>
-    <hyperlink ref="A322" r:id="rId471536"/>
-    <hyperlink ref="A323" r:id="rId471537"/>
-    <hyperlink ref="A324" r:id="rId471538"/>
-    <hyperlink ref="A325" r:id="rId471539"/>
-    <hyperlink ref="A326" r:id="rId471540"/>
-    <hyperlink ref="A327" r:id="rId471541"/>
-    <hyperlink ref="A328" r:id="rId471542"/>
-    <hyperlink ref="A329" r:id="rId471543"/>
-    <hyperlink ref="A330" r:id="rId471544"/>
-    <hyperlink ref="A331" r:id="rId471545"/>
-    <hyperlink ref="A332" r:id="rId471546"/>
-    <hyperlink ref="A333" r:id="rId471547"/>
-    <hyperlink ref="A334" r:id="rId471548"/>
-    <hyperlink ref="A335" r:id="rId471549"/>
-    <hyperlink ref="A336" r:id="rId471550"/>
-    <hyperlink ref="A337" r:id="rId471551"/>
-    <hyperlink ref="A338" r:id="rId471552"/>
-    <hyperlink ref="A339" r:id="rId471553"/>
-    <hyperlink ref="A340" r:id="rId471554"/>
-    <hyperlink ref="A341" r:id="rId471555"/>
-    <hyperlink ref="A342" r:id="rId471556"/>
-    <hyperlink ref="A343" r:id="rId471557"/>
-    <hyperlink ref="A344" r:id="rId471558"/>
-    <hyperlink ref="A345" r:id="rId471559"/>
-    <hyperlink ref="A346" r:id="rId471560"/>
-    <hyperlink ref="A347" r:id="rId471561"/>
-    <hyperlink ref="A348" r:id="rId471562"/>
-    <hyperlink ref="A349" r:id="rId471563"/>
-    <hyperlink ref="A350" r:id="rId471564"/>
-    <hyperlink ref="A351" r:id="rId471565"/>
-    <hyperlink ref="A352" r:id="rId471566"/>
-    <hyperlink ref="A353" r:id="rId471567"/>
-    <hyperlink ref="A354" r:id="rId471568"/>
-    <hyperlink ref="A355" r:id="rId471569"/>
-    <hyperlink ref="A356" r:id="rId471570"/>
-    <hyperlink ref="A357" r:id="rId471571"/>
-    <hyperlink ref="A358" r:id="rId471572"/>
-    <hyperlink ref="A359" r:id="rId471573"/>
-    <hyperlink ref="A360" r:id="rId471574"/>
-    <hyperlink ref="A361" r:id="rId471575"/>
-    <hyperlink ref="A362" r:id="rId471576"/>
-    <hyperlink ref="A363" r:id="rId471577"/>
-    <hyperlink ref="A364" r:id="rId471578"/>
-    <hyperlink ref="A365" r:id="rId471579"/>
-    <hyperlink ref="A366" r:id="rId471580"/>
-    <hyperlink ref="A367" r:id="rId471581"/>
-    <hyperlink ref="A368" r:id="rId471582"/>
-    <hyperlink ref="A369" r:id="rId471583"/>
-    <hyperlink ref="A370" r:id="rId471584"/>
-    <hyperlink ref="A371" r:id="rId471585"/>
-    <hyperlink ref="A372" r:id="rId471586"/>
-    <hyperlink ref="A373" r:id="rId471587"/>
-    <hyperlink ref="A374" r:id="rId471588"/>
-    <hyperlink ref="A375" r:id="rId471589"/>
-    <hyperlink ref="A376" r:id="rId471590"/>
-    <hyperlink ref="A377" r:id="rId471591"/>
-    <hyperlink ref="A378" r:id="rId471592"/>
-    <hyperlink ref="A379" r:id="rId471593"/>
-    <hyperlink ref="A380" r:id="rId471594"/>
-    <hyperlink ref="A381" r:id="rId471595"/>
-    <hyperlink ref="A382" r:id="rId471596"/>
-    <hyperlink ref="A383" r:id="rId471597"/>
-    <hyperlink ref="A384" r:id="rId471598"/>
-    <hyperlink ref="A385" r:id="rId471599"/>
-    <hyperlink ref="A386" r:id="rId471600"/>
-    <hyperlink ref="A387" r:id="rId471601"/>
-    <hyperlink ref="A388" r:id="rId471602"/>
-    <hyperlink ref="A389" r:id="rId471603"/>
-    <hyperlink ref="A390" r:id="rId471604"/>
-    <hyperlink ref="A391" r:id="rId471605"/>
-    <hyperlink ref="A392" r:id="rId471606"/>
-    <hyperlink ref="A393" r:id="rId471607"/>
-    <hyperlink ref="A394" r:id="rId471608"/>
-    <hyperlink ref="A395" r:id="rId471609"/>
-    <hyperlink ref="A396" r:id="rId471610"/>
-    <hyperlink ref="A397" r:id="rId471611"/>
-    <hyperlink ref="A398" r:id="rId471612"/>
-    <hyperlink ref="A399" r:id="rId471613"/>
-    <hyperlink ref="A400" r:id="rId471614"/>
-    <hyperlink ref="A401" r:id="rId471615"/>
-    <hyperlink ref="A402" r:id="rId471616"/>
-    <hyperlink ref="A403" r:id="rId471617"/>
-    <hyperlink ref="A404" r:id="rId471618"/>
-    <hyperlink ref="A405" r:id="rId471619"/>
-    <hyperlink ref="A406" r:id="rId471620"/>
-    <hyperlink ref="A407" r:id="rId471621"/>
-    <hyperlink ref="A408" r:id="rId471622"/>
-    <hyperlink ref="A409" r:id="rId471623"/>
-    <hyperlink ref="A410" r:id="rId471624"/>
-    <hyperlink ref="A411" r:id="rId471625"/>
-    <hyperlink ref="A412" r:id="rId471626"/>
-    <hyperlink ref="A413" r:id="rId471627"/>
-    <hyperlink ref="A414" r:id="rId471628"/>
-    <hyperlink ref="A415" r:id="rId471629"/>
-    <hyperlink ref="A416" r:id="rId471630"/>
-    <hyperlink ref="A417" r:id="rId471631"/>
-    <hyperlink ref="A418" r:id="rId471632"/>
-    <hyperlink ref="A419" r:id="rId471633"/>
-    <hyperlink ref="A420" r:id="rId471634"/>
-    <hyperlink ref="A421" r:id="rId471635"/>
-    <hyperlink ref="A422" r:id="rId471636"/>
-    <hyperlink ref="A423" r:id="rId471637"/>
-    <hyperlink ref="A424" r:id="rId471638"/>
-    <hyperlink ref="A425" r:id="rId471639"/>
-    <hyperlink ref="A426" r:id="rId471640"/>
-    <hyperlink ref="A427" r:id="rId471641"/>
-    <hyperlink ref="A428" r:id="rId471642"/>
-    <hyperlink ref="A429" r:id="rId471643"/>
-    <hyperlink ref="A430" r:id="rId471644"/>
-    <hyperlink ref="A431" r:id="rId471645"/>
-    <hyperlink ref="A432" r:id="rId471646"/>
-    <hyperlink ref="A433" r:id="rId471647"/>
-    <hyperlink ref="A434" r:id="rId471648"/>
-    <hyperlink ref="A435" r:id="rId471649"/>
-    <hyperlink ref="A436" r:id="rId471650"/>
-    <hyperlink ref="A437" r:id="rId471651"/>
-    <hyperlink ref="A438" r:id="rId471652"/>
-    <hyperlink ref="A439" r:id="rId471653"/>
-    <hyperlink ref="A440" r:id="rId471654"/>
-    <hyperlink ref="A441" r:id="rId471655"/>
-    <hyperlink ref="A442" r:id="rId471656"/>
-    <hyperlink ref="A443" r:id="rId471657"/>
-    <hyperlink ref="A444" r:id="rId471658"/>
-    <hyperlink ref="A445" r:id="rId471659"/>
-    <hyperlink ref="A446" r:id="rId471660"/>
-    <hyperlink ref="A447" r:id="rId471661"/>
-    <hyperlink ref="A448" r:id="rId471662"/>
-    <hyperlink ref="A449" r:id="rId471663"/>
-    <hyperlink ref="A450" r:id="rId471664"/>
-    <hyperlink ref="A451" r:id="rId471665"/>
-    <hyperlink ref="A452" r:id="rId471666"/>
-    <hyperlink ref="A453" r:id="rId471667"/>
-    <hyperlink ref="A454" r:id="rId471668"/>
-    <hyperlink ref="A455" r:id="rId471669"/>
-    <hyperlink ref="A456" r:id="rId471670"/>
-    <hyperlink ref="A457" r:id="rId471671"/>
-    <hyperlink ref="A458" r:id="rId471672"/>
-    <hyperlink ref="A459" r:id="rId471673"/>
-    <hyperlink ref="A460" r:id="rId471674"/>
-    <hyperlink ref="A461" r:id="rId471675"/>
-    <hyperlink ref="A462" r:id="rId471676"/>
-    <hyperlink ref="A463" r:id="rId471677"/>
-    <hyperlink ref="A464" r:id="rId471678"/>
-    <hyperlink ref="A465" r:id="rId471679"/>
-    <hyperlink ref="A466" r:id="rId471680"/>
-    <hyperlink ref="A467" r:id="rId471681"/>
-    <hyperlink ref="A468" r:id="rId471682"/>
-    <hyperlink ref="A469" r:id="rId471683"/>
-    <hyperlink ref="A470" r:id="rId471684"/>
-    <hyperlink ref="A471" r:id="rId471685"/>
-    <hyperlink ref="A472" r:id="rId471686"/>
-    <hyperlink ref="A473" r:id="rId471687"/>
-    <hyperlink ref="A474" r:id="rId471688"/>
-    <hyperlink ref="A475" r:id="rId471689"/>
-    <hyperlink ref="A476" r:id="rId471690"/>
-    <hyperlink ref="A477" r:id="rId471691"/>
-    <hyperlink ref="A478" r:id="rId471692"/>
-    <hyperlink ref="A479" r:id="rId471693"/>
-    <hyperlink ref="A480" r:id="rId471694"/>
-    <hyperlink ref="A481" r:id="rId471695"/>
-    <hyperlink ref="A482" r:id="rId471696"/>
-    <hyperlink ref="A483" r:id="rId471697"/>
-    <hyperlink ref="A484" r:id="rId471698"/>
-    <hyperlink ref="A485" r:id="rId471699"/>
-    <hyperlink ref="A486" r:id="rId471700"/>
-    <hyperlink ref="A487" r:id="rId471701"/>
-    <hyperlink ref="A488" r:id="rId471702"/>
-    <hyperlink ref="A489" r:id="rId471703"/>
-    <hyperlink ref="A490" r:id="rId471704"/>
-    <hyperlink ref="A491" r:id="rId471705"/>
-    <hyperlink ref="A492" r:id="rId471706"/>
-    <hyperlink ref="A493" r:id="rId471707"/>
-    <hyperlink ref="A494" r:id="rId471708"/>
-    <hyperlink ref="A495" r:id="rId471709"/>
-    <hyperlink ref="A496" r:id="rId471710"/>
-    <hyperlink ref="A497" r:id="rId471711"/>
-    <hyperlink ref="A498" r:id="rId471712"/>
-    <hyperlink ref="A499" r:id="rId471713"/>
-    <hyperlink ref="A500" r:id="rId471714"/>
-    <hyperlink ref="A501" r:id="rId471715"/>
-    <hyperlink ref="A502" r:id="rId471716"/>
-    <hyperlink ref="A503" r:id="rId471717"/>
-    <hyperlink ref="A504" r:id="rId471718"/>
-    <hyperlink ref="A505" r:id="rId471719"/>
-    <hyperlink ref="A506" r:id="rId471720"/>
-    <hyperlink ref="A507" r:id="rId471721"/>
-    <hyperlink ref="A508" r:id="rId471722"/>
-    <hyperlink ref="A509" r:id="rId471723"/>
-    <hyperlink ref="A510" r:id="rId471724"/>
-    <hyperlink ref="A511" r:id="rId471725"/>
-    <hyperlink ref="A512" r:id="rId471726"/>
-    <hyperlink ref="A513" r:id="rId471727"/>
-    <hyperlink ref="A514" r:id="rId471728"/>
-    <hyperlink ref="A515" r:id="rId471729"/>
-    <hyperlink ref="A516" r:id="rId471730"/>
-    <hyperlink ref="A517" r:id="rId471731"/>
-    <hyperlink ref="A518" r:id="rId471732"/>
-    <hyperlink ref="A519" r:id="rId471733"/>
-    <hyperlink ref="A520" r:id="rId471734"/>
-    <hyperlink ref="A521" r:id="rId471735"/>
-    <hyperlink ref="A522" r:id="rId471736"/>
-    <hyperlink ref="A523" r:id="rId471737"/>
-    <hyperlink ref="A524" r:id="rId471738"/>
-    <hyperlink ref="A525" r:id="rId471739"/>
-    <hyperlink ref="A526" r:id="rId471740"/>
-    <hyperlink ref="A527" r:id="rId471741"/>
-    <hyperlink ref="A528" r:id="rId471742"/>
-    <hyperlink ref="A529" r:id="rId471743"/>
-    <hyperlink ref="A530" r:id="rId471744"/>
-    <hyperlink ref="A531" r:id="rId471745"/>
-    <hyperlink ref="A532" r:id="rId471746"/>
-    <hyperlink ref="A533" r:id="rId471747"/>
-    <hyperlink ref="A534" r:id="rId471748"/>
-    <hyperlink ref="A535" r:id="rId471749"/>
-    <hyperlink ref="A536" r:id="rId471750"/>
-    <hyperlink ref="A537" r:id="rId471751"/>
-    <hyperlink ref="A538" r:id="rId471752"/>
-    <hyperlink ref="A539" r:id="rId471753"/>
-    <hyperlink ref="A540" r:id="rId471754"/>
-    <hyperlink ref="A541" r:id="rId471755"/>
-    <hyperlink ref="A542" r:id="rId471756"/>
-    <hyperlink ref="A543" r:id="rId471757"/>
-    <hyperlink ref="A544" r:id="rId471758"/>
-    <hyperlink ref="A545" r:id="rId471759"/>
-    <hyperlink ref="A546" r:id="rId471760"/>
-    <hyperlink ref="A547" r:id="rId471761"/>
-    <hyperlink ref="A548" r:id="rId471762"/>
-    <hyperlink ref="A549" r:id="rId471763"/>
-    <hyperlink ref="A550" r:id="rId471764"/>
-    <hyperlink ref="A551" r:id="rId471765"/>
-    <hyperlink ref="A552" r:id="rId471766"/>
-    <hyperlink ref="A553" r:id="rId471767"/>
-    <hyperlink ref="A554" r:id="rId471768"/>
-    <hyperlink ref="A555" r:id="rId471769"/>
-    <hyperlink ref="A556" r:id="rId471770"/>
-    <hyperlink ref="A557" r:id="rId471771"/>
-    <hyperlink ref="A558" r:id="rId471772"/>
-    <hyperlink ref="A559" r:id="rId471773"/>
-    <hyperlink ref="A560" r:id="rId471774"/>
-    <hyperlink ref="A561" r:id="rId471775"/>
-    <hyperlink ref="A562" r:id="rId471776"/>
-    <hyperlink ref="A563" r:id="rId471777"/>
-    <hyperlink ref="A564" r:id="rId471778"/>
-    <hyperlink ref="A565" r:id="rId471779"/>
-    <hyperlink ref="A566" r:id="rId471780"/>
-    <hyperlink ref="A567" r:id="rId471781"/>
-    <hyperlink ref="A568" r:id="rId471782"/>
-    <hyperlink ref="A569" r:id="rId471783"/>
-    <hyperlink ref="A570" r:id="rId471784"/>
-    <hyperlink ref="A571" r:id="rId471785"/>
-    <hyperlink ref="A572" r:id="rId471786"/>
-    <hyperlink ref="A573" r:id="rId471787"/>
-    <hyperlink ref="A574" r:id="rId471788"/>
-    <hyperlink ref="A575" r:id="rId471789"/>
-    <hyperlink ref="A576" r:id="rId471790"/>
-    <hyperlink ref="A577" r:id="rId471791"/>
-    <hyperlink ref="A578" r:id="rId471792"/>
-    <hyperlink ref="A579" r:id="rId471793"/>
-    <hyperlink ref="A580" r:id="rId471794"/>
-    <hyperlink ref="A581" r:id="rId471795"/>
-    <hyperlink ref="A582" r:id="rId471796"/>
-    <hyperlink ref="A583" r:id="rId471797"/>
-    <hyperlink ref="A584" r:id="rId471798"/>
-    <hyperlink ref="A585" r:id="rId471799"/>
-    <hyperlink ref="A586" r:id="rId471800"/>
-    <hyperlink ref="A587" r:id="rId471801"/>
-    <hyperlink ref="A588" r:id="rId471802"/>
-    <hyperlink ref="A589" r:id="rId471803"/>
-    <hyperlink ref="A590" r:id="rId471804"/>
-    <hyperlink ref="A591" r:id="rId471805"/>
-    <hyperlink ref="A592" r:id="rId471806"/>
-    <hyperlink ref="A593" r:id="rId471807"/>
-    <hyperlink ref="A594" r:id="rId471808"/>
-    <hyperlink ref="A595" r:id="rId471809"/>
-    <hyperlink ref="A596" r:id="rId471810"/>
-    <hyperlink ref="A597" r:id="rId471811"/>
-    <hyperlink ref="A598" r:id="rId471812"/>
-    <hyperlink ref="A599" r:id="rId471813"/>
-    <hyperlink ref="A600" r:id="rId471814"/>
-    <hyperlink ref="A601" r:id="rId471815"/>
-    <hyperlink ref="A602" r:id="rId471816"/>
-    <hyperlink ref="A603" r:id="rId471817"/>
-    <hyperlink ref="A604" r:id="rId471818"/>
-    <hyperlink ref="A605" r:id="rId471819"/>
-    <hyperlink ref="A606" r:id="rId471820"/>
-    <hyperlink ref="A607" r:id="rId471821"/>
-    <hyperlink ref="A608" r:id="rId471822"/>
-    <hyperlink ref="A609" r:id="rId471823"/>
-    <hyperlink ref="A610" r:id="rId471824"/>
-    <hyperlink ref="A611" r:id="rId471825"/>
-    <hyperlink ref="A612" r:id="rId471826"/>
-    <hyperlink ref="A613" r:id="rId471827"/>
-    <hyperlink ref="A614" r:id="rId471828"/>
-    <hyperlink ref="A615" r:id="rId471829"/>
-    <hyperlink ref="A616" r:id="rId471830"/>
-    <hyperlink ref="A617" r:id="rId471831"/>
-    <hyperlink ref="A618" r:id="rId471832"/>
-    <hyperlink ref="A619" r:id="rId471833"/>
-    <hyperlink ref="A620" r:id="rId471834"/>
-    <hyperlink ref="A621" r:id="rId471835"/>
-    <hyperlink ref="A622" r:id="rId471836"/>
-    <hyperlink ref="A623" r:id="rId471837"/>
-    <hyperlink ref="A624" r:id="rId471838"/>
-    <hyperlink ref="A625" r:id="rId471839"/>
-    <hyperlink ref="A626" r:id="rId471840"/>
-    <hyperlink ref="A627" r:id="rId471841"/>
-    <hyperlink ref="A628" r:id="rId471842"/>
-    <hyperlink ref="A629" r:id="rId471843"/>
-    <hyperlink ref="A630" r:id="rId471844"/>
-    <hyperlink ref="A631" r:id="rId471845"/>
-    <hyperlink ref="A632" r:id="rId471846"/>
+    <hyperlink ref="A7" r:id="rId17737"/>
+    <hyperlink ref="A8" r:id="rId17738"/>
+    <hyperlink ref="A9" r:id="rId17739"/>
+    <hyperlink ref="A10" r:id="rId17740"/>
+    <hyperlink ref="A11" r:id="rId17741"/>
+    <hyperlink ref="A12" r:id="rId17742"/>
+    <hyperlink ref="A13" r:id="rId17743"/>
+    <hyperlink ref="A14" r:id="rId17744"/>
+    <hyperlink ref="A15" r:id="rId17745"/>
+    <hyperlink ref="A16" r:id="rId17746"/>
+    <hyperlink ref="A17" r:id="rId17747"/>
+    <hyperlink ref="A18" r:id="rId17748"/>
+    <hyperlink ref="A19" r:id="rId17749"/>
+    <hyperlink ref="A20" r:id="rId17750"/>
+    <hyperlink ref="A21" r:id="rId17751"/>
+    <hyperlink ref="A22" r:id="rId17752"/>
+    <hyperlink ref="A23" r:id="rId17753"/>
+    <hyperlink ref="A24" r:id="rId17754"/>
+    <hyperlink ref="A25" r:id="rId17755"/>
+    <hyperlink ref="A26" r:id="rId17756"/>
+    <hyperlink ref="A27" r:id="rId17757"/>
+    <hyperlink ref="A28" r:id="rId17758"/>
+    <hyperlink ref="A29" r:id="rId17759"/>
+    <hyperlink ref="A30" r:id="rId17760"/>
+    <hyperlink ref="A31" r:id="rId17761"/>
+    <hyperlink ref="A32" r:id="rId17762"/>
+    <hyperlink ref="A33" r:id="rId17763"/>
+    <hyperlink ref="A34" r:id="rId17764"/>
+    <hyperlink ref="A35" r:id="rId17765"/>
+    <hyperlink ref="A36" r:id="rId17766"/>
+    <hyperlink ref="A37" r:id="rId17767"/>
+    <hyperlink ref="A38" r:id="rId17768"/>
+    <hyperlink ref="A39" r:id="rId17769"/>
+    <hyperlink ref="A40" r:id="rId17770"/>
+    <hyperlink ref="A41" r:id="rId17771"/>
+    <hyperlink ref="A42" r:id="rId17772"/>
+    <hyperlink ref="A43" r:id="rId17773"/>
+    <hyperlink ref="A44" r:id="rId17774"/>
+    <hyperlink ref="A45" r:id="rId17775"/>
+    <hyperlink ref="A46" r:id="rId17776"/>
+    <hyperlink ref="A47" r:id="rId17777"/>
+    <hyperlink ref="A48" r:id="rId17778"/>
+    <hyperlink ref="A49" r:id="rId17779"/>
+    <hyperlink ref="A50" r:id="rId17780"/>
+    <hyperlink ref="A51" r:id="rId17781"/>
+    <hyperlink ref="A52" r:id="rId17782"/>
+    <hyperlink ref="A53" r:id="rId17783"/>
+    <hyperlink ref="A54" r:id="rId17784"/>
+    <hyperlink ref="A55" r:id="rId17785"/>
+    <hyperlink ref="A56" r:id="rId17786"/>
+    <hyperlink ref="A57" r:id="rId17787"/>
+    <hyperlink ref="A58" r:id="rId17788"/>
+    <hyperlink ref="A59" r:id="rId17789"/>
+    <hyperlink ref="A60" r:id="rId17790"/>
+    <hyperlink ref="A61" r:id="rId17791"/>
+    <hyperlink ref="A62" r:id="rId17792"/>
+    <hyperlink ref="A63" r:id="rId17793"/>
+    <hyperlink ref="A64" r:id="rId17794"/>
+    <hyperlink ref="A65" r:id="rId17795"/>
+    <hyperlink ref="A66" r:id="rId17796"/>
+    <hyperlink ref="A67" r:id="rId17797"/>
+    <hyperlink ref="A68" r:id="rId17798"/>
+    <hyperlink ref="A69" r:id="rId17799"/>
+    <hyperlink ref="A70" r:id="rId17800"/>
+    <hyperlink ref="A71" r:id="rId17801"/>
+    <hyperlink ref="A72" r:id="rId17802"/>
+    <hyperlink ref="A73" r:id="rId17803"/>
+    <hyperlink ref="A74" r:id="rId17804"/>
+    <hyperlink ref="A75" r:id="rId17805"/>
+    <hyperlink ref="A76" r:id="rId17806"/>
+    <hyperlink ref="A77" r:id="rId17807"/>
+    <hyperlink ref="A78" r:id="rId17808"/>
+    <hyperlink ref="A79" r:id="rId17809"/>
+    <hyperlink ref="A80" r:id="rId17810"/>
+    <hyperlink ref="A81" r:id="rId17811"/>
+    <hyperlink ref="A82" r:id="rId17812"/>
+    <hyperlink ref="A83" r:id="rId17813"/>
+    <hyperlink ref="A84" r:id="rId17814"/>
+    <hyperlink ref="A85" r:id="rId17815"/>
+    <hyperlink ref="A86" r:id="rId17816"/>
+    <hyperlink ref="A87" r:id="rId17817"/>
+    <hyperlink ref="A88" r:id="rId17818"/>
+    <hyperlink ref="A89" r:id="rId17819"/>
+    <hyperlink ref="A90" r:id="rId17820"/>
+    <hyperlink ref="A91" r:id="rId17821"/>
+    <hyperlink ref="A92" r:id="rId17822"/>
+    <hyperlink ref="A93" r:id="rId17823"/>
+    <hyperlink ref="A94" r:id="rId17824"/>
+    <hyperlink ref="A95" r:id="rId17825"/>
+    <hyperlink ref="A96" r:id="rId17826"/>
+    <hyperlink ref="A97" r:id="rId17827"/>
+    <hyperlink ref="A98" r:id="rId17828"/>
+    <hyperlink ref="A99" r:id="rId17829"/>
+    <hyperlink ref="A100" r:id="rId17830"/>
+    <hyperlink ref="A101" r:id="rId17831"/>
+    <hyperlink ref="A102" r:id="rId17832"/>
+    <hyperlink ref="A103" r:id="rId17833"/>
+    <hyperlink ref="A104" r:id="rId17834"/>
+    <hyperlink ref="A105" r:id="rId17835"/>
+    <hyperlink ref="A106" r:id="rId17836"/>
+    <hyperlink ref="A107" r:id="rId17837"/>
+    <hyperlink ref="A108" r:id="rId17838"/>
+    <hyperlink ref="A109" r:id="rId17839"/>
+    <hyperlink ref="A110" r:id="rId17840"/>
+    <hyperlink ref="A111" r:id="rId17841"/>
+    <hyperlink ref="A112" r:id="rId17842"/>
+    <hyperlink ref="A113" r:id="rId17843"/>
+    <hyperlink ref="A114" r:id="rId17844"/>
+    <hyperlink ref="A115" r:id="rId17845"/>
+    <hyperlink ref="A116" r:id="rId17846"/>
+    <hyperlink ref="A117" r:id="rId17847"/>
+    <hyperlink ref="A118" r:id="rId17848"/>
+    <hyperlink ref="A119" r:id="rId17849"/>
+    <hyperlink ref="A120" r:id="rId17850"/>
+    <hyperlink ref="A121" r:id="rId17851"/>
+    <hyperlink ref="A122" r:id="rId17852"/>
+    <hyperlink ref="A123" r:id="rId17853"/>
+    <hyperlink ref="A124" r:id="rId17854"/>
+    <hyperlink ref="A125" r:id="rId17855"/>
+    <hyperlink ref="A126" r:id="rId17856"/>
+    <hyperlink ref="A127" r:id="rId17857"/>
+    <hyperlink ref="A128" r:id="rId17858"/>
+    <hyperlink ref="A129" r:id="rId17859"/>
+    <hyperlink ref="A130" r:id="rId17860"/>
+    <hyperlink ref="A131" r:id="rId17861"/>
+    <hyperlink ref="A132" r:id="rId17862"/>
+    <hyperlink ref="A133" r:id="rId17863"/>
+    <hyperlink ref="A134" r:id="rId17864"/>
+    <hyperlink ref="A135" r:id="rId17865"/>
+    <hyperlink ref="A136" r:id="rId17866"/>
+    <hyperlink ref="A137" r:id="rId17867"/>
+    <hyperlink ref="A138" r:id="rId17868"/>
+    <hyperlink ref="A139" r:id="rId17869"/>
+    <hyperlink ref="A140" r:id="rId17870"/>
+    <hyperlink ref="A141" r:id="rId17871"/>
+    <hyperlink ref="A142" r:id="rId17872"/>
+    <hyperlink ref="A143" r:id="rId17873"/>
+    <hyperlink ref="A144" r:id="rId17874"/>
+    <hyperlink ref="A145" r:id="rId17875"/>
+    <hyperlink ref="A146" r:id="rId17876"/>
+    <hyperlink ref="A147" r:id="rId17877"/>
+    <hyperlink ref="A148" r:id="rId17878"/>
+    <hyperlink ref="A149" r:id="rId17879"/>
+    <hyperlink ref="A150" r:id="rId17880"/>
+    <hyperlink ref="A151" r:id="rId17881"/>
+    <hyperlink ref="A152" r:id="rId17882"/>
+    <hyperlink ref="A153" r:id="rId17883"/>
+    <hyperlink ref="A154" r:id="rId17884"/>
+    <hyperlink ref="A155" r:id="rId17885"/>
+    <hyperlink ref="A156" r:id="rId17886"/>
+    <hyperlink ref="A157" r:id="rId17887"/>
+    <hyperlink ref="A158" r:id="rId17888"/>
+    <hyperlink ref="A159" r:id="rId17889"/>
+    <hyperlink ref="A160" r:id="rId17890"/>
+    <hyperlink ref="A161" r:id="rId17891"/>
+    <hyperlink ref="A162" r:id="rId17892"/>
+    <hyperlink ref="A163" r:id="rId17893"/>
+    <hyperlink ref="A164" r:id="rId17894"/>
+    <hyperlink ref="A165" r:id="rId17895"/>
+    <hyperlink ref="A166" r:id="rId17896"/>
+    <hyperlink ref="A167" r:id="rId17897"/>
+    <hyperlink ref="A168" r:id="rId17898"/>
+    <hyperlink ref="A169" r:id="rId17899"/>
+    <hyperlink ref="A170" r:id="rId17900"/>
+    <hyperlink ref="A171" r:id="rId17901"/>
+    <hyperlink ref="A172" r:id="rId17902"/>
+    <hyperlink ref="A173" r:id="rId17903"/>
+    <hyperlink ref="A174" r:id="rId17904"/>
+    <hyperlink ref="A175" r:id="rId17905"/>
+    <hyperlink ref="A176" r:id="rId17906"/>
+    <hyperlink ref="A177" r:id="rId17907"/>
+    <hyperlink ref="A178" r:id="rId17908"/>
+    <hyperlink ref="A179" r:id="rId17909"/>
+    <hyperlink ref="A180" r:id="rId17910"/>
+    <hyperlink ref="A181" r:id="rId17911"/>
+    <hyperlink ref="A182" r:id="rId17912"/>
+    <hyperlink ref="A183" r:id="rId17913"/>
+    <hyperlink ref="A184" r:id="rId17914"/>
+    <hyperlink ref="A185" r:id="rId17915"/>
+    <hyperlink ref="A186" r:id="rId17916"/>
+    <hyperlink ref="A187" r:id="rId17917"/>
+    <hyperlink ref="A188" r:id="rId17918"/>
+    <hyperlink ref="A189" r:id="rId17919"/>
+    <hyperlink ref="A190" r:id="rId17920"/>
+    <hyperlink ref="A191" r:id="rId17921"/>
+    <hyperlink ref="A192" r:id="rId17922"/>
+    <hyperlink ref="A193" r:id="rId17923"/>
+    <hyperlink ref="A194" r:id="rId17924"/>
+    <hyperlink ref="A195" r:id="rId17925"/>
+    <hyperlink ref="A196" r:id="rId17926"/>
+    <hyperlink ref="A197" r:id="rId17927"/>
+    <hyperlink ref="A198" r:id="rId17928"/>
+    <hyperlink ref="A199" r:id="rId17929"/>
+    <hyperlink ref="A200" r:id="rId17930"/>
+    <hyperlink ref="A201" r:id="rId17931"/>
+    <hyperlink ref="A202" r:id="rId17932"/>
+    <hyperlink ref="A203" r:id="rId17933"/>
+    <hyperlink ref="A204" r:id="rId17934"/>
+    <hyperlink ref="A205" r:id="rId17935"/>
+    <hyperlink ref="A206" r:id="rId17936"/>
+    <hyperlink ref="A207" r:id="rId17937"/>
+    <hyperlink ref="A208" r:id="rId17938"/>
+    <hyperlink ref="A209" r:id="rId17939"/>
+    <hyperlink ref="A210" r:id="rId17940"/>
+    <hyperlink ref="A211" r:id="rId17941"/>
+    <hyperlink ref="A212" r:id="rId17942"/>
+    <hyperlink ref="A213" r:id="rId17943"/>
+    <hyperlink ref="A214" r:id="rId17944"/>
+    <hyperlink ref="A215" r:id="rId17945"/>
+    <hyperlink ref="A216" r:id="rId17946"/>
+    <hyperlink ref="A217" r:id="rId17947"/>
+    <hyperlink ref="A218" r:id="rId17948"/>
+    <hyperlink ref="A219" r:id="rId17949"/>
+    <hyperlink ref="A220" r:id="rId17950"/>
+    <hyperlink ref="A221" r:id="rId17951"/>
+    <hyperlink ref="A222" r:id="rId17952"/>
+    <hyperlink ref="A223" r:id="rId17953"/>
+    <hyperlink ref="A224" r:id="rId17954"/>
+    <hyperlink ref="A225" r:id="rId17955"/>
+    <hyperlink ref="A226" r:id="rId17956"/>
+    <hyperlink ref="A227" r:id="rId17957"/>
+    <hyperlink ref="A228" r:id="rId17958"/>
+    <hyperlink ref="A229" r:id="rId17959"/>
+    <hyperlink ref="A230" r:id="rId17960"/>
+    <hyperlink ref="A231" r:id="rId17961"/>
+    <hyperlink ref="A232" r:id="rId17962"/>
+    <hyperlink ref="A233" r:id="rId17963"/>
+    <hyperlink ref="A234" r:id="rId17964"/>
+    <hyperlink ref="A235" r:id="rId17965"/>
+    <hyperlink ref="A236" r:id="rId17966"/>
+    <hyperlink ref="A237" r:id="rId17967"/>
+    <hyperlink ref="A238" r:id="rId17968"/>
+    <hyperlink ref="A239" r:id="rId17969"/>
+    <hyperlink ref="A240" r:id="rId17970"/>
+    <hyperlink ref="A241" r:id="rId17971"/>
+    <hyperlink ref="A242" r:id="rId17972"/>
+    <hyperlink ref="A243" r:id="rId17973"/>
+    <hyperlink ref="A244" r:id="rId17974"/>
+    <hyperlink ref="A245" r:id="rId17975"/>
+    <hyperlink ref="A246" r:id="rId17976"/>
+    <hyperlink ref="A247" r:id="rId17977"/>
+    <hyperlink ref="A248" r:id="rId17978"/>
+    <hyperlink ref="A249" r:id="rId17979"/>
+    <hyperlink ref="A250" r:id="rId17980"/>
+    <hyperlink ref="A251" r:id="rId17981"/>
+    <hyperlink ref="A252" r:id="rId17982"/>
+    <hyperlink ref="A253" r:id="rId17983"/>
+    <hyperlink ref="A254" r:id="rId17984"/>
+    <hyperlink ref="A255" r:id="rId17985"/>
+    <hyperlink ref="A256" r:id="rId17986"/>
+    <hyperlink ref="A257" r:id="rId17987"/>
+    <hyperlink ref="A258" r:id="rId17988"/>
+    <hyperlink ref="A259" r:id="rId17989"/>
+    <hyperlink ref="A260" r:id="rId17990"/>
+    <hyperlink ref="A261" r:id="rId17991"/>
+    <hyperlink ref="A262" r:id="rId17992"/>
+    <hyperlink ref="A263" r:id="rId17993"/>
+    <hyperlink ref="A264" r:id="rId17994"/>
+    <hyperlink ref="A265" r:id="rId17995"/>
+    <hyperlink ref="A266" r:id="rId17996"/>
+    <hyperlink ref="A267" r:id="rId17997"/>
+    <hyperlink ref="A268" r:id="rId17998"/>
+    <hyperlink ref="A269" r:id="rId17999"/>
+    <hyperlink ref="A270" r:id="rId18000"/>
+    <hyperlink ref="A271" r:id="rId18001"/>
+    <hyperlink ref="A272" r:id="rId18002"/>
+    <hyperlink ref="A273" r:id="rId18003"/>
+    <hyperlink ref="A274" r:id="rId18004"/>
+    <hyperlink ref="A275" r:id="rId18005"/>
+    <hyperlink ref="A276" r:id="rId18006"/>
+    <hyperlink ref="A277" r:id="rId18007"/>
+    <hyperlink ref="A278" r:id="rId18008"/>
+    <hyperlink ref="A279" r:id="rId18009"/>
+    <hyperlink ref="A280" r:id="rId18010"/>
+    <hyperlink ref="A281" r:id="rId18011"/>
+    <hyperlink ref="A282" r:id="rId18012"/>
+    <hyperlink ref="A283" r:id="rId18013"/>
+    <hyperlink ref="A284" r:id="rId18014"/>
+    <hyperlink ref="A285" r:id="rId18015"/>
+    <hyperlink ref="A286" r:id="rId18016"/>
+    <hyperlink ref="A287" r:id="rId18017"/>
+    <hyperlink ref="A288" r:id="rId18018"/>
+    <hyperlink ref="A289" r:id="rId18019"/>
+    <hyperlink ref="A290" r:id="rId18020"/>
+    <hyperlink ref="A291" r:id="rId18021"/>
+    <hyperlink ref="A292" r:id="rId18022"/>
+    <hyperlink ref="A293" r:id="rId18023"/>
+    <hyperlink ref="A294" r:id="rId18024"/>
+    <hyperlink ref="A295" r:id="rId18025"/>
+    <hyperlink ref="A296" r:id="rId18026"/>
+    <hyperlink ref="A297" r:id="rId18027"/>
+    <hyperlink ref="A298" r:id="rId18028"/>
+    <hyperlink ref="A299" r:id="rId18029"/>
+    <hyperlink ref="A300" r:id="rId18030"/>
+    <hyperlink ref="A301" r:id="rId18031"/>
+    <hyperlink ref="A302" r:id="rId18032"/>
+    <hyperlink ref="A303" r:id="rId18033"/>
+    <hyperlink ref="A304" r:id="rId18034"/>
+    <hyperlink ref="A305" r:id="rId18035"/>
+    <hyperlink ref="A306" r:id="rId18036"/>
+    <hyperlink ref="A307" r:id="rId18037"/>
+    <hyperlink ref="A308" r:id="rId18038"/>
+    <hyperlink ref="A309" r:id="rId18039"/>
+    <hyperlink ref="A310" r:id="rId18040"/>
+    <hyperlink ref="A311" r:id="rId18041"/>
+    <hyperlink ref="A312" r:id="rId18042"/>
+    <hyperlink ref="A313" r:id="rId18043"/>
+    <hyperlink ref="A314" r:id="rId18044"/>
+    <hyperlink ref="A315" r:id="rId18045"/>
+    <hyperlink ref="A316" r:id="rId18046"/>
+    <hyperlink ref="A317" r:id="rId18047"/>
+    <hyperlink ref="A318" r:id="rId18048"/>
+    <hyperlink ref="A319" r:id="rId18049"/>
+    <hyperlink ref="A320" r:id="rId18050"/>
+    <hyperlink ref="A321" r:id="rId18051"/>
+    <hyperlink ref="A322" r:id="rId18052"/>
+    <hyperlink ref="A323" r:id="rId18053"/>
+    <hyperlink ref="A324" r:id="rId18054"/>
+    <hyperlink ref="A325" r:id="rId18055"/>
+    <hyperlink ref="A326" r:id="rId18056"/>
+    <hyperlink ref="A327" r:id="rId18057"/>
+    <hyperlink ref="A328" r:id="rId18058"/>
+    <hyperlink ref="A329" r:id="rId18059"/>
+    <hyperlink ref="A330" r:id="rId18060"/>
+    <hyperlink ref="A331" r:id="rId18061"/>
+    <hyperlink ref="A332" r:id="rId18062"/>
+    <hyperlink ref="A333" r:id="rId18063"/>
+    <hyperlink ref="A334" r:id="rId18064"/>
+    <hyperlink ref="A335" r:id="rId18065"/>
+    <hyperlink ref="A336" r:id="rId18066"/>
+    <hyperlink ref="A337" r:id="rId18067"/>
+    <hyperlink ref="A338" r:id="rId18068"/>
+    <hyperlink ref="A339" r:id="rId18069"/>
+    <hyperlink ref="A340" r:id="rId18070"/>
+    <hyperlink ref="A341" r:id="rId18071"/>
+    <hyperlink ref="A342" r:id="rId18072"/>
+    <hyperlink ref="A343" r:id="rId18073"/>
+    <hyperlink ref="A344" r:id="rId18074"/>
+    <hyperlink ref="A345" r:id="rId18075"/>
+    <hyperlink ref="A346" r:id="rId18076"/>
+    <hyperlink ref="A347" r:id="rId18077"/>
+    <hyperlink ref="A348" r:id="rId18078"/>
+    <hyperlink ref="A349" r:id="rId18079"/>
+    <hyperlink ref="A350" r:id="rId18080"/>
+    <hyperlink ref="A351" r:id="rId18081"/>
+    <hyperlink ref="A352" r:id="rId18082"/>
+    <hyperlink ref="A353" r:id="rId18083"/>
+    <hyperlink ref="A354" r:id="rId18084"/>
+    <hyperlink ref="A355" r:id="rId18085"/>
+    <hyperlink ref="A356" r:id="rId18086"/>
+    <hyperlink ref="A357" r:id="rId18087"/>
+    <hyperlink ref="A358" r:id="rId18088"/>
+    <hyperlink ref="A359" r:id="rId18089"/>
+    <hyperlink ref="A360" r:id="rId18090"/>
+    <hyperlink ref="A361" r:id="rId18091"/>
+    <hyperlink ref="A362" r:id="rId18092"/>
+    <hyperlink ref="A363" r:id="rId18093"/>
+    <hyperlink ref="A364" r:id="rId18094"/>
+    <hyperlink ref="A365" r:id="rId18095"/>
+    <hyperlink ref="A366" r:id="rId18096"/>
+    <hyperlink ref="A367" r:id="rId18097"/>
+    <hyperlink ref="A368" r:id="rId18098"/>
+    <hyperlink ref="A369" r:id="rId18099"/>
+    <hyperlink ref="A370" r:id="rId18100"/>
+    <hyperlink ref="A371" r:id="rId18101"/>
+    <hyperlink ref="A372" r:id="rId18102"/>
+    <hyperlink ref="A373" r:id="rId18103"/>
+    <hyperlink ref="A374" r:id="rId18104"/>
+    <hyperlink ref="A375" r:id="rId18105"/>
+    <hyperlink ref="A376" r:id="rId18106"/>
+    <hyperlink ref="A377" r:id="rId18107"/>
+    <hyperlink ref="A378" r:id="rId18108"/>
+    <hyperlink ref="A379" r:id="rId18109"/>
+    <hyperlink ref="A380" r:id="rId18110"/>
+    <hyperlink ref="A381" r:id="rId18111"/>
+    <hyperlink ref="A382" r:id="rId18112"/>
+    <hyperlink ref="A383" r:id="rId18113"/>
+    <hyperlink ref="A384" r:id="rId18114"/>
+    <hyperlink ref="A385" r:id="rId18115"/>
+    <hyperlink ref="A386" r:id="rId18116"/>
+    <hyperlink ref="A387" r:id="rId18117"/>
+    <hyperlink ref="A388" r:id="rId18118"/>
+    <hyperlink ref="A389" r:id="rId18119"/>
+    <hyperlink ref="A390" r:id="rId18120"/>
+    <hyperlink ref="A391" r:id="rId18121"/>
+    <hyperlink ref="A392" r:id="rId18122"/>
+    <hyperlink ref="A393" r:id="rId18123"/>
+    <hyperlink ref="A394" r:id="rId18124"/>
+    <hyperlink ref="A395" r:id="rId18125"/>
+    <hyperlink ref="A396" r:id="rId18126"/>
+    <hyperlink ref="A397" r:id="rId18127"/>
+    <hyperlink ref="A398" r:id="rId18128"/>
+    <hyperlink ref="A399" r:id="rId18129"/>
+    <hyperlink ref="A400" r:id="rId18130"/>
+    <hyperlink ref="A401" r:id="rId18131"/>
+    <hyperlink ref="A402" r:id="rId18132"/>
+    <hyperlink ref="A403" r:id="rId18133"/>
+    <hyperlink ref="A404" r:id="rId18134"/>
+    <hyperlink ref="A405" r:id="rId18135"/>
+    <hyperlink ref="A406" r:id="rId18136"/>
+    <hyperlink ref="A407" r:id="rId18137"/>
+    <hyperlink ref="A408" r:id="rId18138"/>
+    <hyperlink ref="A409" r:id="rId18139"/>
+    <hyperlink ref="A410" r:id="rId18140"/>
+    <hyperlink ref="A411" r:id="rId18141"/>
+    <hyperlink ref="A412" r:id="rId18142"/>
+    <hyperlink ref="A413" r:id="rId18143"/>
+    <hyperlink ref="A414" r:id="rId18144"/>
+    <hyperlink ref="A415" r:id="rId18145"/>
+    <hyperlink ref="A416" r:id="rId18146"/>
+    <hyperlink ref="A417" r:id="rId18147"/>
+    <hyperlink ref="A418" r:id="rId18148"/>
+    <hyperlink ref="A419" r:id="rId18149"/>
+    <hyperlink ref="A420" r:id="rId18150"/>
+    <hyperlink ref="A421" r:id="rId18151"/>
+    <hyperlink ref="A422" r:id="rId18152"/>
+    <hyperlink ref="A423" r:id="rId18153"/>
+    <hyperlink ref="A424" r:id="rId18154"/>
+    <hyperlink ref="A425" r:id="rId18155"/>
+    <hyperlink ref="A426" r:id="rId18156"/>
+    <hyperlink ref="A427" r:id="rId18157"/>
+    <hyperlink ref="A428" r:id="rId18158"/>
+    <hyperlink ref="A429" r:id="rId18159"/>
+    <hyperlink ref="A430" r:id="rId18160"/>
+    <hyperlink ref="A431" r:id="rId18161"/>
+    <hyperlink ref="A432" r:id="rId18162"/>
+    <hyperlink ref="A433" r:id="rId18163"/>
+    <hyperlink ref="A434" r:id="rId18164"/>
+    <hyperlink ref="A435" r:id="rId18165"/>
+    <hyperlink ref="A436" r:id="rId18166"/>
+    <hyperlink ref="A437" r:id="rId18167"/>
+    <hyperlink ref="A438" r:id="rId18168"/>
+    <hyperlink ref="A439" r:id="rId18169"/>
+    <hyperlink ref="A440" r:id="rId18170"/>
+    <hyperlink ref="A441" r:id="rId18171"/>
+    <hyperlink ref="A442" r:id="rId18172"/>
+    <hyperlink ref="A443" r:id="rId18173"/>
+    <hyperlink ref="A444" r:id="rId18174"/>
+    <hyperlink ref="A445" r:id="rId18175"/>
+    <hyperlink ref="A446" r:id="rId18176"/>
+    <hyperlink ref="A447" r:id="rId18177"/>
+    <hyperlink ref="A448" r:id="rId18178"/>
+    <hyperlink ref="A449" r:id="rId18179"/>
+    <hyperlink ref="A450" r:id="rId18180"/>
+    <hyperlink ref="A451" r:id="rId18181"/>
+    <hyperlink ref="A452" r:id="rId18182"/>
+    <hyperlink ref="A453" r:id="rId18183"/>
+    <hyperlink ref="A454" r:id="rId18184"/>
+    <hyperlink ref="A455" r:id="rId18185"/>
+    <hyperlink ref="A456" r:id="rId18186"/>
+    <hyperlink ref="A457" r:id="rId18187"/>
+    <hyperlink ref="A458" r:id="rId18188"/>
+    <hyperlink ref="A459" r:id="rId18189"/>
+    <hyperlink ref="A460" r:id="rId18190"/>
+    <hyperlink ref="A461" r:id="rId18191"/>
+    <hyperlink ref="A462" r:id="rId18192"/>
+    <hyperlink ref="A463" r:id="rId18193"/>
+    <hyperlink ref="A464" r:id="rId18194"/>
+    <hyperlink ref="A465" r:id="rId18195"/>
+    <hyperlink ref="A466" r:id="rId18196"/>
+    <hyperlink ref="A467" r:id="rId18197"/>
+    <hyperlink ref="A468" r:id="rId18198"/>
+    <hyperlink ref="A469" r:id="rId18199"/>
+    <hyperlink ref="A470" r:id="rId18200"/>
+    <hyperlink ref="A471" r:id="rId18201"/>
+    <hyperlink ref="A472" r:id="rId18202"/>
+    <hyperlink ref="A473" r:id="rId18203"/>
+    <hyperlink ref="A474" r:id="rId18204"/>
+    <hyperlink ref="A475" r:id="rId18205"/>
+    <hyperlink ref="A476" r:id="rId18206"/>
+    <hyperlink ref="A477" r:id="rId18207"/>
+    <hyperlink ref="A478" r:id="rId18208"/>
+    <hyperlink ref="A479" r:id="rId18209"/>
+    <hyperlink ref="A480" r:id="rId18210"/>
+    <hyperlink ref="A481" r:id="rId18211"/>
+    <hyperlink ref="A482" r:id="rId18212"/>
+    <hyperlink ref="A483" r:id="rId18213"/>
+    <hyperlink ref="A484" r:id="rId18214"/>
+    <hyperlink ref="A485" r:id="rId18215"/>
+    <hyperlink ref="A486" r:id="rId18216"/>
+    <hyperlink ref="A487" r:id="rId18217"/>
+    <hyperlink ref="A488" r:id="rId18218"/>
+    <hyperlink ref="A489" r:id="rId18219"/>
+    <hyperlink ref="A490" r:id="rId18220"/>
+    <hyperlink ref="A491" r:id="rId18221"/>
+    <hyperlink ref="A492" r:id="rId18222"/>
+    <hyperlink ref="A493" r:id="rId18223"/>
+    <hyperlink ref="A494" r:id="rId18224"/>
+    <hyperlink ref="A495" r:id="rId18225"/>
+    <hyperlink ref="A496" r:id="rId18226"/>
+    <hyperlink ref="A497" r:id="rId18227"/>
+    <hyperlink ref="A498" r:id="rId18228"/>
+    <hyperlink ref="A499" r:id="rId18229"/>
+    <hyperlink ref="A500" r:id="rId18230"/>
+    <hyperlink ref="A501" r:id="rId18231"/>
+    <hyperlink ref="A502" r:id="rId18232"/>
+    <hyperlink ref="A503" r:id="rId18233"/>
+    <hyperlink ref="A504" r:id="rId18234"/>
+    <hyperlink ref="A505" r:id="rId18235"/>
+    <hyperlink ref="A506" r:id="rId18236"/>
+    <hyperlink ref="A507" r:id="rId18237"/>
+    <hyperlink ref="A508" r:id="rId18238"/>
+    <hyperlink ref="A509" r:id="rId18239"/>
+    <hyperlink ref="A510" r:id="rId18240"/>
+    <hyperlink ref="A511" r:id="rId18241"/>
+    <hyperlink ref="A512" r:id="rId18242"/>
+    <hyperlink ref="A513" r:id="rId18243"/>
+    <hyperlink ref="A514" r:id="rId18244"/>
+    <hyperlink ref="A515" r:id="rId18245"/>
+    <hyperlink ref="A516" r:id="rId18246"/>
+    <hyperlink ref="A517" r:id="rId18247"/>
+    <hyperlink ref="A518" r:id="rId18248"/>
+    <hyperlink ref="A519" r:id="rId18249"/>
+    <hyperlink ref="A520" r:id="rId18250"/>
+    <hyperlink ref="A521" r:id="rId18251"/>
+    <hyperlink ref="A522" r:id="rId18252"/>
+    <hyperlink ref="A523" r:id="rId18253"/>
+    <hyperlink ref="A524" r:id="rId18254"/>
+    <hyperlink ref="A525" r:id="rId18255"/>
+    <hyperlink ref="A526" r:id="rId18256"/>
+    <hyperlink ref="A527" r:id="rId18257"/>
+    <hyperlink ref="A528" r:id="rId18258"/>
+    <hyperlink ref="A529" r:id="rId18259"/>
+    <hyperlink ref="A530" r:id="rId18260"/>
+    <hyperlink ref="A531" r:id="rId18261"/>
+    <hyperlink ref="A532" r:id="rId18262"/>
+    <hyperlink ref="A533" r:id="rId18263"/>
+    <hyperlink ref="A534" r:id="rId18264"/>
+    <hyperlink ref="A535" r:id="rId18265"/>
+    <hyperlink ref="A536" r:id="rId18266"/>
+    <hyperlink ref="A537" r:id="rId18267"/>
+    <hyperlink ref="A538" r:id="rId18268"/>
+    <hyperlink ref="A539" r:id="rId18269"/>
+    <hyperlink ref="A540" r:id="rId18270"/>
+    <hyperlink ref="A541" r:id="rId18271"/>
+    <hyperlink ref="A542" r:id="rId18272"/>
+    <hyperlink ref="A543" r:id="rId18273"/>
+    <hyperlink ref="A544" r:id="rId18274"/>
+    <hyperlink ref="A545" r:id="rId18275"/>
+    <hyperlink ref="A546" r:id="rId18276"/>
+    <hyperlink ref="A547" r:id="rId18277"/>
+    <hyperlink ref="A548" r:id="rId18278"/>
+    <hyperlink ref="A549" r:id="rId18279"/>
+    <hyperlink ref="A550" r:id="rId18280"/>
+    <hyperlink ref="A551" r:id="rId18281"/>
+    <hyperlink ref="A552" r:id="rId18282"/>
+    <hyperlink ref="A553" r:id="rId18283"/>
+    <hyperlink ref="A554" r:id="rId18284"/>
+    <hyperlink ref="A555" r:id="rId18285"/>
+    <hyperlink ref="A556" r:id="rId18286"/>
+    <hyperlink ref="A557" r:id="rId18287"/>
+    <hyperlink ref="A558" r:id="rId18288"/>
+    <hyperlink ref="A559" r:id="rId18289"/>
+    <hyperlink ref="A560" r:id="rId18290"/>
+    <hyperlink ref="A561" r:id="rId18291"/>
+    <hyperlink ref="A562" r:id="rId18292"/>
+    <hyperlink ref="A563" r:id="rId18293"/>
+    <hyperlink ref="A564" r:id="rId18294"/>
+    <hyperlink ref="A565" r:id="rId18295"/>
+    <hyperlink ref="A566" r:id="rId18296"/>
+    <hyperlink ref="A567" r:id="rId18297"/>
+    <hyperlink ref="A568" r:id="rId18298"/>
+    <hyperlink ref="A569" r:id="rId18299"/>
+    <hyperlink ref="A570" r:id="rId18300"/>
+    <hyperlink ref="A571" r:id="rId18301"/>
+    <hyperlink ref="A572" r:id="rId18302"/>
+    <hyperlink ref="A573" r:id="rId18303"/>
+    <hyperlink ref="A574" r:id="rId18304"/>
+    <hyperlink ref="A575" r:id="rId18305"/>
+    <hyperlink ref="A576" r:id="rId18306"/>
+    <hyperlink ref="A577" r:id="rId18307"/>
+    <hyperlink ref="A578" r:id="rId18308"/>
+    <hyperlink ref="A579" r:id="rId18309"/>
+    <hyperlink ref="A580" r:id="rId18310"/>
+    <hyperlink ref="A581" r:id="rId18311"/>
+    <hyperlink ref="A582" r:id="rId18312"/>
+    <hyperlink ref="A583" r:id="rId18313"/>
+    <hyperlink ref="A584" r:id="rId18314"/>
+    <hyperlink ref="A585" r:id="rId18315"/>
+    <hyperlink ref="A586" r:id="rId18316"/>
+    <hyperlink ref="A587" r:id="rId18317"/>
+    <hyperlink ref="A588" r:id="rId18318"/>
+    <hyperlink ref="A589" r:id="rId18319"/>
+    <hyperlink ref="A590" r:id="rId18320"/>
+    <hyperlink ref="A591" r:id="rId18321"/>
+    <hyperlink ref="A592" r:id="rId18322"/>
+    <hyperlink ref="A593" r:id="rId18323"/>
+    <hyperlink ref="A594" r:id="rId18324"/>
+    <hyperlink ref="A595" r:id="rId18325"/>
+    <hyperlink ref="A596" r:id="rId18326"/>
+    <hyperlink ref="A597" r:id="rId18327"/>
+    <hyperlink ref="A598" r:id="rId18328"/>
+    <hyperlink ref="A599" r:id="rId18329"/>
+    <hyperlink ref="A600" r:id="rId18330"/>
+    <hyperlink ref="A601" r:id="rId18331"/>
+    <hyperlink ref="A602" r:id="rId18332"/>
+    <hyperlink ref="A603" r:id="rId18333"/>
+    <hyperlink ref="A604" r:id="rId18334"/>
+    <hyperlink ref="A605" r:id="rId18335"/>
+    <hyperlink ref="A606" r:id="rId18336"/>
+    <hyperlink ref="A607" r:id="rId18337"/>
+    <hyperlink ref="A608" r:id="rId18338"/>
+    <hyperlink ref="A609" r:id="rId18339"/>
+    <hyperlink ref="A610" r:id="rId18340"/>
+    <hyperlink ref="A611" r:id="rId18341"/>
+    <hyperlink ref="A612" r:id="rId18342"/>
+    <hyperlink ref="A613" r:id="rId18343"/>
+    <hyperlink ref="A614" r:id="rId18344"/>
+    <hyperlink ref="A615" r:id="rId18345"/>
+    <hyperlink ref="A616" r:id="rId18346"/>
+    <hyperlink ref="A617" r:id="rId18347"/>
+    <hyperlink ref="A618" r:id="rId18348"/>
+    <hyperlink ref="A619" r:id="rId18349"/>
+    <hyperlink ref="A620" r:id="rId18350"/>
+    <hyperlink ref="A621" r:id="rId18351"/>
+    <hyperlink ref="A622" r:id="rId18352"/>
+    <hyperlink ref="A623" r:id="rId18353"/>
+    <hyperlink ref="A624" r:id="rId18354"/>
+    <hyperlink ref="A625" r:id="rId18355"/>
+    <hyperlink ref="A626" r:id="rId18356"/>
+    <hyperlink ref="A627" r:id="rId18357"/>
+    <hyperlink ref="A628" r:id="rId18358"/>
+    <hyperlink ref="A629" r:id="rId18359"/>
+    <hyperlink ref="A630" r:id="rId18360"/>
+    <hyperlink ref="A631" r:id="rId18361"/>
+    <hyperlink ref="A632" r:id="rId18362"/>
   </hyperlinks>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter/>
